--- a/gstdatabase/GSTR-3B-2023-2024.xlsx
+++ b/gstdatabase/GSTR-3B-2023-2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976BE507-149D-4303-AF47-0A39A49B64BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B429FA-4B40-4C67-B66C-C3418DC13A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>FINANCIAL YEAR 2023-2024</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -1131,14 +1131,14 @@
       </c>
       <c r="O10" s="4">
         <f>P10-N10</f>
-        <v>23854</v>
+        <v>23855</v>
       </c>
       <c r="P10" s="14">
-        <v>120207</v>
+        <v>120208</v>
       </c>
       <c r="Q10" s="5">
         <f>P10/M10</f>
-        <v>0.9978500157720851</v>
+        <v>0.99785831686949011</v>
       </c>
       <c r="R10" s="8">
         <v>70979</v>
@@ -1165,14 +1165,14 @@
       </c>
       <c r="Y10" s="4">
         <f>Z10-X10</f>
-        <v>14964</v>
+        <v>14967</v>
       </c>
       <c r="Z10" s="14">
-        <v>72992</v>
+        <v>72995</v>
       </c>
       <c r="AA10" s="5">
         <f>Z10/W10</f>
-        <v>0.99514642526040242</v>
+        <v>0.99518732617112937</v>
       </c>
       <c r="AB10" s="8">
         <v>123554</v>
@@ -1182,14 +1182,14 @@
       </c>
       <c r="AD10" s="4">
         <f>AE10-AC10</f>
-        <v>25351</v>
+        <v>25354</v>
       </c>
       <c r="AE10" s="14">
-        <v>123355</v>
+        <v>123358</v>
       </c>
       <c r="AF10" s="5">
         <f>AE10/AB10</f>
-        <v>0.99838936821147028</v>
+        <v>0.99841364909270436</v>
       </c>
       <c r="AG10" s="8">
         <v>71950</v>
@@ -1199,14 +1199,14 @@
       </c>
       <c r="AI10" s="4">
         <f>AJ10-AH10</f>
-        <v>15070</v>
+        <v>15073</v>
       </c>
       <c r="AJ10" s="14">
-        <v>72018</v>
+        <v>72021</v>
       </c>
       <c r="AK10" s="5">
         <f>AJ10/AG10</f>
-        <v>1.0009451007644197</v>
+        <v>1.0009867963863794</v>
       </c>
       <c r="AL10" s="8">
         <v>73532</v>
@@ -1216,14 +1216,14 @@
       </c>
       <c r="AN10" s="4">
         <f>AO10-AM10</f>
-        <v>14453</v>
+        <v>14458</v>
       </c>
       <c r="AO10" s="14">
-        <v>72988</v>
+        <v>72993</v>
       </c>
       <c r="AP10" s="5">
         <f>AO10/AL10</f>
-        <v>0.99260186041451337</v>
+        <v>0.99266985802099761</v>
       </c>
       <c r="AQ10" s="8">
         <v>125499</v>
@@ -1233,14 +1233,14 @@
       </c>
       <c r="AS10" s="4">
         <f>AT10-AR10</f>
-        <v>22109</v>
+        <v>22115</v>
       </c>
       <c r="AT10" s="14">
-        <v>125748</v>
+        <v>125754</v>
       </c>
       <c r="AU10" s="5">
         <f>AT10/AQ10</f>
-        <v>1.0019840795544188</v>
+        <v>1.0020318887003083</v>
       </c>
       <c r="AV10" s="8">
         <v>72481</v>
@@ -1250,14 +1250,14 @@
       </c>
       <c r="AX10" s="4">
         <f>AY10-AW10</f>
-        <v>14009</v>
+        <v>14013</v>
       </c>
       <c r="AY10" s="14">
-        <v>72381</v>
+        <v>72385</v>
       </c>
       <c r="AZ10" s="5">
         <f>AY10/AV10</f>
-        <v>0.99862032808598111</v>
+        <v>0.99867551496254192</v>
       </c>
       <c r="BA10" s="8">
         <v>73790</v>
@@ -1267,14 +1267,14 @@
       </c>
       <c r="BC10" s="4">
         <f>BD10-BB10</f>
-        <v>13151</v>
+        <v>13155</v>
       </c>
       <c r="BD10" s="14">
-        <v>73305</v>
+        <v>73309</v>
       </c>
       <c r="BE10" s="5">
         <f>BD10/BA10</f>
-        <v>0.99342729367122917</v>
+        <v>0.99348150155847681</v>
       </c>
       <c r="BF10" s="8">
         <v>128129</v>
@@ -1284,14 +1284,14 @@
       </c>
       <c r="BH10" s="4">
         <f>BI10-BG10</f>
-        <v>30707</v>
+        <v>30714</v>
       </c>
       <c r="BI10" s="14">
-        <v>127907</v>
+        <v>127914</v>
       </c>
       <c r="BJ10" s="5">
         <f>BI10/BF10</f>
-        <v>0.99826737116499775</v>
+        <v>0.99832200360574108</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1309,14 +1309,14 @@
       </c>
       <c r="E11" s="4">
         <f t="shared" ref="E11:E47" si="0">F11-D11</f>
-        <v>8354</v>
+        <v>8356</v>
       </c>
       <c r="F11" s="14">
-        <v>45072</v>
+        <v>45074</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>1.0125353821269714</v>
+        <v>1.0125803118120142</v>
       </c>
       <c r="H11" s="8">
         <v>46110</v>
@@ -1326,14 +1326,14 @@
       </c>
       <c r="J11" s="4">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>8440</v>
+        <v>8441</v>
       </c>
       <c r="K11" s="14">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>1.0002602472348732</v>
+        <v>1.0002819345044458</v>
       </c>
       <c r="M11" s="8">
         <v>102242</v>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="O11" s="4">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>17901</v>
+        <v>17902</v>
       </c>
       <c r="P11" s="14">
-        <v>102367</v>
+        <v>102368</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>1.001222589542458</v>
+        <v>1.0012323702587977</v>
       </c>
       <c r="R11" s="8">
         <v>44890</v>
@@ -1360,14 +1360,14 @@
       </c>
       <c r="T11" s="4">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>8660</v>
+        <v>8661</v>
       </c>
       <c r="U11" s="14">
-        <v>45097</v>
+        <v>45098</v>
       </c>
       <c r="V11" s="5">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>1.0046112719982179</v>
+        <v>1.0046335486745377</v>
       </c>
       <c r="W11" s="8">
         <v>46425</v>
@@ -1377,14 +1377,14 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>8819</v>
+        <v>8821</v>
       </c>
       <c r="Z11" s="14">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.99134087237479807</v>
+        <v>0.99138395261173939</v>
       </c>
       <c r="AB11" s="8">
         <v>103964</v>
@@ -1394,14 +1394,14 @@
       </c>
       <c r="AD11" s="4">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>17253</v>
+        <v>17256</v>
       </c>
       <c r="AE11" s="14">
-        <v>104138</v>
+        <v>104141</v>
       </c>
       <c r="AF11" s="5">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>1.0016736562656303</v>
+        <v>1.0017025124081413</v>
       </c>
       <c r="AG11" s="8">
         <v>45569</v>
@@ -1411,14 +1411,14 @@
       </c>
       <c r="AI11" s="4">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>8689</v>
+        <v>8691</v>
       </c>
       <c r="AJ11" s="14">
-        <v>45678</v>
+        <v>45680</v>
       </c>
       <c r="AK11" s="5">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>1.0023919770019092</v>
+        <v>1.0024358664881827</v>
       </c>
       <c r="AL11" s="8">
         <v>46951</v>
@@ -1428,14 +1428,14 @@
       </c>
       <c r="AN11" s="4">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>7787</v>
+        <v>7791</v>
       </c>
       <c r="AO11" s="14">
-        <v>46372</v>
+        <v>46376</v>
       </c>
       <c r="AP11" s="5">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.98766799429192131</v>
+        <v>0.98775318949543145</v>
       </c>
       <c r="AQ11" s="8">
         <v>105644</v>
@@ -1445,14 +1445,14 @@
       </c>
       <c r="AS11" s="4">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>15143</v>
+        <v>15147</v>
       </c>
       <c r="AT11" s="14">
-        <v>105857</v>
+        <v>105861</v>
       </c>
       <c r="AU11" s="5">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>1.002016205368975</v>
+        <v>1.002054068380599</v>
       </c>
       <c r="AV11" s="8">
         <v>46072</v>
@@ -1462,14 +1462,14 @@
       </c>
       <c r="AX11" s="4">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>7556</v>
+        <v>7558</v>
       </c>
       <c r="AY11" s="14">
-        <v>46206</v>
+        <v>46208</v>
       </c>
       <c r="AZ11" s="5">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>1.0029084910574753</v>
+        <v>1.002951901371766</v>
       </c>
       <c r="BA11" s="8">
         <v>47252</v>
@@ -1479,14 +1479,14 @@
       </c>
       <c r="BC11" s="4">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>7191</v>
+        <v>7193</v>
       </c>
       <c r="BD11" s="14">
-        <v>47006</v>
+        <v>47008</v>
       </c>
       <c r="BE11" s="5">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.99479387115889273</v>
+        <v>0.99483619740963347</v>
       </c>
       <c r="BF11" s="8">
         <v>107665</v>
@@ -1496,14 +1496,14 @@
       </c>
       <c r="BH11" s="4">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>19654</v>
+        <v>19659</v>
       </c>
       <c r="BI11" s="14">
-        <v>107544</v>
+        <v>107549</v>
       </c>
       <c r="BJ11" s="5">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.99887614359355403</v>
+        <v>0.99892258394092792</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="0"/>
-        <v>24309</v>
+        <v>24313</v>
       </c>
       <c r="F12" s="14">
-        <v>165520</v>
+        <v>165524</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.99728866662649873</v>
+        <v>0.99731276736759655</v>
       </c>
       <c r="H12" s="8">
         <v>170538</v>
@@ -1538,14 +1538,14 @@
       </c>
       <c r="J12" s="4">
         <f t="shared" si="2"/>
-        <v>24748</v>
+        <v>24753</v>
       </c>
       <c r="K12" s="14">
-        <v>168573</v>
+        <v>168578</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="3"/>
-        <v>0.98847764134679661</v>
+        <v>0.98850696032555796</v>
       </c>
       <c r="M12" s="8">
         <v>344875</v>
@@ -1555,14 +1555,14 @@
       </c>
       <c r="O12" s="4">
         <f t="shared" si="4"/>
-        <v>54202</v>
+        <v>54206</v>
       </c>
       <c r="P12" s="14">
-        <v>343204</v>
+        <v>343208</v>
       </c>
       <c r="Q12" s="5">
         <f t="shared" si="5"/>
-        <v>0.99515476621964483</v>
+        <v>0.99516636462486407</v>
       </c>
       <c r="R12" s="8">
         <v>167705</v>
@@ -1572,14 +1572,14 @@
       </c>
       <c r="T12" s="4">
         <f t="shared" si="6"/>
-        <v>27009</v>
+        <v>27014</v>
       </c>
       <c r="U12" s="14">
-        <v>167151</v>
+        <v>167156</v>
       </c>
       <c r="V12" s="5">
         <f t="shared" si="7"/>
-        <v>0.99669658030470176</v>
+        <v>0.9967263945618795</v>
       </c>
       <c r="W12" s="8">
         <v>171864</v>
@@ -1589,14 +1589,14 @@
       </c>
       <c r="Y12" s="4">
         <f t="shared" si="8"/>
-        <v>27610</v>
+        <v>27614</v>
       </c>
       <c r="Z12" s="14">
-        <v>170068</v>
+        <v>170072</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="9"/>
-        <v>0.98954987664665084</v>
+        <v>0.98957315086347342</v>
       </c>
       <c r="AB12" s="8">
         <v>349048</v>
@@ -1606,14 +1606,14 @@
       </c>
       <c r="AD12" s="4">
         <f t="shared" si="10"/>
-        <v>58561</v>
+        <v>58565</v>
       </c>
       <c r="AE12" s="14">
-        <v>348030</v>
+        <v>348034</v>
       </c>
       <c r="AF12" s="5">
         <f t="shared" si="11"/>
-        <v>0.99708349567967725</v>
+        <v>0.99709495542160387</v>
       </c>
       <c r="AG12" s="8">
         <v>170526</v>
@@ -1623,14 +1623,14 @@
       </c>
       <c r="AI12" s="4">
         <f t="shared" si="12"/>
-        <v>27747</v>
+        <v>27750</v>
       </c>
       <c r="AJ12" s="14">
-        <v>170191</v>
+        <v>170194</v>
       </c>
       <c r="AK12" s="5">
         <f t="shared" si="13"/>
-        <v>0.99803549018917936</v>
+        <v>0.9980530828143509</v>
       </c>
       <c r="AL12" s="8">
         <v>174892</v>
@@ -1640,14 +1640,14 @@
       </c>
       <c r="AN12" s="4">
         <f t="shared" si="14"/>
-        <v>25080</v>
+        <v>25084</v>
       </c>
       <c r="AO12" s="14">
-        <v>172406</v>
+        <v>172410</v>
       </c>
       <c r="AP12" s="5">
         <f t="shared" si="15"/>
-        <v>0.98578551334537889</v>
+        <v>0.9858083846030693</v>
       </c>
       <c r="AQ12" s="8">
         <v>353589</v>
@@ -1657,14 +1657,14 @@
       </c>
       <c r="AS12" s="4">
         <f t="shared" si="16"/>
-        <v>50897</v>
+        <v>50902</v>
       </c>
       <c r="AT12" s="14">
-        <v>352807</v>
+        <v>352812</v>
       </c>
       <c r="AU12" s="5">
         <f t="shared" si="17"/>
-        <v>0.99778839273846187</v>
+        <v>0.99780253344985281</v>
       </c>
       <c r="AV12" s="8">
         <v>172980</v>
@@ -1674,14 +1674,14 @@
       </c>
       <c r="AX12" s="4">
         <f t="shared" si="18"/>
-        <v>24629</v>
+        <v>24634</v>
       </c>
       <c r="AY12" s="14">
-        <v>172346</v>
+        <v>172351</v>
       </c>
       <c r="AZ12" s="5">
         <f t="shared" si="19"/>
-        <v>0.99633483639727138</v>
+        <v>0.99636374147300266</v>
       </c>
       <c r="BA12" s="8">
         <v>177212</v>
@@ -1691,14 +1691,14 @@
       </c>
       <c r="BC12" s="4">
         <f t="shared" si="20"/>
-        <v>24044</v>
+        <v>24048</v>
       </c>
       <c r="BD12" s="14">
-        <v>174795</v>
+        <v>174799</v>
       </c>
       <c r="BE12" s="5">
         <f t="shared" si="21"/>
-        <v>0.98636096878315238</v>
+        <v>0.98638354061801681</v>
       </c>
       <c r="BF12" s="8">
         <v>359260</v>
@@ -1708,14 +1708,14 @@
       </c>
       <c r="BH12" s="4">
         <f t="shared" si="22"/>
-        <v>65717</v>
+        <v>65722</v>
       </c>
       <c r="BI12" s="14">
-        <v>357423</v>
+        <v>357428</v>
       </c>
       <c r="BJ12" s="5">
         <f t="shared" si="23"/>
-        <v>0.99488671157379061</v>
+        <v>0.99490062907086785</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1945,14 +1945,14 @@
       </c>
       <c r="E14" s="4">
         <f t="shared" si="0"/>
-        <v>18162</v>
+        <v>18163</v>
       </c>
       <c r="F14" s="14">
-        <v>85321</v>
+        <v>85322</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="1"/>
-        <v>0.99927386013609265</v>
+        <v>0.99928557206938151</v>
       </c>
       <c r="H14" s="8">
         <v>88261</v>
@@ -1962,14 +1962,14 @@
       </c>
       <c r="J14" s="4">
         <f t="shared" si="2"/>
-        <v>18275</v>
+        <v>18276</v>
       </c>
       <c r="K14" s="14">
-        <v>87144</v>
+        <v>87145</v>
       </c>
       <c r="L14" s="5">
         <f t="shared" si="3"/>
-        <v>0.98734435367829509</v>
+        <v>0.98735568371081228</v>
       </c>
       <c r="M14" s="8">
         <v>157146</v>
@@ -1979,14 +1979,14 @@
       </c>
       <c r="O14" s="4">
         <f t="shared" si="4"/>
-        <v>32114</v>
+        <v>32115</v>
       </c>
       <c r="P14" s="14">
-        <v>155515</v>
+        <v>155516</v>
       </c>
       <c r="Q14" s="5">
         <f t="shared" si="5"/>
-        <v>0.98962111666857577</v>
+        <v>0.98962748017766922</v>
       </c>
       <c r="R14" s="8">
         <v>86469</v>
@@ -1996,14 +1996,14 @@
       </c>
       <c r="T14" s="4">
         <f t="shared" si="6"/>
-        <v>18349</v>
+        <v>18350</v>
       </c>
       <c r="U14" s="14">
-        <v>85414</v>
+        <v>85415</v>
       </c>
       <c r="V14" s="5">
         <f t="shared" si="7"/>
-        <v>0.98779909562964763</v>
+        <v>0.98781066046791333</v>
       </c>
       <c r="W14" s="8">
         <v>88169</v>
@@ -2013,14 +2013,14 @@
       </c>
       <c r="Y14" s="4">
         <f t="shared" si="8"/>
-        <v>17866</v>
+        <v>17867</v>
       </c>
       <c r="Z14" s="14">
-        <v>86574</v>
+        <v>86575</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="9"/>
-        <v>0.98190974151912802</v>
+        <v>0.98192108337397499</v>
       </c>
       <c r="AB14" s="8">
         <v>157930</v>
@@ -2030,14 +2030,14 @@
       </c>
       <c r="AD14" s="4">
         <f t="shared" si="10"/>
-        <v>33762</v>
+        <v>33766</v>
       </c>
       <c r="AE14" s="14">
-        <v>157187</v>
+        <v>157191</v>
       </c>
       <c r="AF14" s="5">
         <f t="shared" si="11"/>
-        <v>0.99529538403089979</v>
+        <v>0.99532071170771863</v>
       </c>
       <c r="AG14" s="8">
         <v>87312</v>
@@ -2047,14 +2047,14 @@
       </c>
       <c r="AI14" s="4">
         <f t="shared" si="12"/>
-        <v>19601</v>
+        <v>19603</v>
       </c>
       <c r="AJ14" s="14">
-        <v>86933</v>
+        <v>86935</v>
       </c>
       <c r="AK14" s="5">
         <f t="shared" si="13"/>
-        <v>0.99565924500641378</v>
+        <v>0.99568215136521898</v>
       </c>
       <c r="AL14" s="8">
         <v>89337</v>
@@ -2064,14 +2064,14 @@
       </c>
       <c r="AN14" s="4">
         <f t="shared" si="14"/>
-        <v>17003</v>
+        <v>17005</v>
       </c>
       <c r="AO14" s="14">
-        <v>87943</v>
+        <v>87945</v>
       </c>
       <c r="AP14" s="5">
         <f t="shared" si="15"/>
-        <v>0.98439616284406239</v>
+        <v>0.98441854998488865</v>
       </c>
       <c r="AQ14" s="8">
         <v>160173</v>
@@ -2081,14 +2081,14 @@
       </c>
       <c r="AS14" s="4">
         <f t="shared" si="16"/>
-        <v>29870</v>
+        <v>29877</v>
       </c>
       <c r="AT14" s="14">
-        <v>160311</v>
+        <v>160318</v>
       </c>
       <c r="AU14" s="5">
         <f t="shared" si="17"/>
-        <v>1.000861568429136</v>
+        <v>1.0009052711755415</v>
       </c>
       <c r="AV14" s="8">
         <v>88523</v>
@@ -2098,14 +2098,14 @@
       </c>
       <c r="AX14" s="4">
         <f t="shared" si="18"/>
-        <v>17233</v>
+        <v>17237</v>
       </c>
       <c r="AY14" s="14">
-        <v>88593</v>
+        <v>88597</v>
       </c>
       <c r="AZ14" s="5">
         <f t="shared" si="19"/>
-        <v>1.0007907549450425</v>
+        <v>1.0008359409419021</v>
       </c>
       <c r="BA14" s="8">
         <v>90782</v>
@@ -2115,14 +2115,14 @@
       </c>
       <c r="BC14" s="4">
         <f t="shared" si="20"/>
-        <v>16198</v>
+        <v>16203</v>
       </c>
       <c r="BD14" s="14">
-        <v>89779</v>
+        <v>89784</v>
       </c>
       <c r="BE14" s="5">
         <f t="shared" si="21"/>
-        <v>0.98895155427287351</v>
+        <v>0.98900663127051613</v>
       </c>
       <c r="BF14" s="8">
         <v>163900</v>
@@ -2132,14 +2132,14 @@
       </c>
       <c r="BH14" s="4">
         <f t="shared" si="22"/>
-        <v>39498</v>
+        <v>39505</v>
       </c>
       <c r="BI14" s="14">
-        <v>162858</v>
+        <v>162865</v>
       </c>
       <c r="BJ14" s="5">
         <f t="shared" si="23"/>
-        <v>0.99364246491763275</v>
+        <v>0.99368517388651612</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2242,14 +2242,14 @@
       </c>
       <c r="AD15" s="4">
         <f t="shared" si="10"/>
-        <v>86723</v>
+        <v>86726</v>
       </c>
       <c r="AE15" s="14">
-        <v>491015</v>
+        <v>491018</v>
       </c>
       <c r="AF15" s="5">
         <f t="shared" si="11"/>
-        <v>0.99057269895579481</v>
+        <v>0.99057875114991689</v>
       </c>
       <c r="AG15" s="8">
         <v>292071</v>
@@ -2259,14 +2259,14 @@
       </c>
       <c r="AI15" s="4">
         <f t="shared" si="12"/>
-        <v>54942</v>
+        <v>54943</v>
       </c>
       <c r="AJ15" s="14">
-        <v>289860</v>
+        <v>289861</v>
       </c>
       <c r="AK15" s="5">
         <f t="shared" si="13"/>
-        <v>0.99242992286122211</v>
+        <v>0.99243334668625094</v>
       </c>
       <c r="AL15" s="8">
         <v>298411</v>
@@ -2276,14 +2276,14 @@
       </c>
       <c r="AN15" s="4">
         <f t="shared" si="14"/>
-        <v>47365</v>
+        <v>47366</v>
       </c>
       <c r="AO15" s="14">
-        <v>293459</v>
+        <v>293460</v>
       </c>
       <c r="AP15" s="5">
         <f t="shared" si="15"/>
-        <v>0.9834054374671175</v>
+        <v>0.9834087885500199</v>
       </c>
       <c r="AQ15" s="8">
         <v>502913</v>
@@ -2293,14 +2293,14 @@
       </c>
       <c r="AS15" s="4">
         <f t="shared" si="16"/>
-        <v>75301</v>
+        <v>75303</v>
       </c>
       <c r="AT15" s="14">
-        <v>498860</v>
+        <v>498862</v>
       </c>
       <c r="AU15" s="5">
         <f t="shared" si="17"/>
-        <v>0.99194095201356891</v>
+        <v>0.99194492884455165</v>
       </c>
       <c r="AV15" s="8">
         <v>298012</v>
@@ -2310,14 +2310,14 @@
       </c>
       <c r="AX15" s="4">
         <f t="shared" si="18"/>
-        <v>47952</v>
+        <v>47954</v>
       </c>
       <c r="AY15" s="14">
-        <v>295219</v>
+        <v>295221</v>
       </c>
       <c r="AZ15" s="5">
         <f t="shared" si="19"/>
-        <v>0.99062789417875785</v>
+        <v>0.9906346053179067</v>
       </c>
       <c r="BA15" s="8">
         <v>303376</v>
@@ -2327,14 +2327,14 @@
       </c>
       <c r="BC15" s="4">
         <f t="shared" si="20"/>
-        <v>45519</v>
+        <v>45522</v>
       </c>
       <c r="BD15" s="14">
-        <v>299097</v>
+        <v>299100</v>
       </c>
       <c r="BE15" s="5">
         <f t="shared" si="21"/>
-        <v>0.98589539053847375</v>
+        <v>0.98590527925742311</v>
       </c>
       <c r="BF15" s="8">
         <v>511329</v>
@@ -2344,14 +2344,14 @@
       </c>
       <c r="BH15" s="4">
         <f t="shared" si="22"/>
-        <v>92303</v>
+        <v>92308</v>
       </c>
       <c r="BI15" s="14">
-        <v>506569</v>
+        <v>506574</v>
       </c>
       <c r="BJ15" s="5">
         <f t="shared" si="23"/>
-        <v>0.99069092502087697</v>
+        <v>0.99070070346098105</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2369,14 +2369,14 @@
       </c>
       <c r="E16" s="4">
         <f t="shared" si="0"/>
-        <v>73115</v>
+        <v>73122</v>
       </c>
       <c r="F16" s="14">
-        <v>427882</v>
+        <v>427889</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="1"/>
-        <v>0.99360711507425081</v>
+        <v>0.99362337013944524</v>
       </c>
       <c r="H16" s="8">
         <v>441093</v>
@@ -2386,14 +2386,14 @@
       </c>
       <c r="J16" s="4">
         <f t="shared" si="2"/>
-        <v>74315</v>
+        <v>74323</v>
       </c>
       <c r="K16" s="14">
-        <v>432700</v>
+        <v>432708</v>
       </c>
       <c r="L16" s="5">
         <f t="shared" si="3"/>
-        <v>0.98097226661951109</v>
+        <v>0.98099040338432031</v>
       </c>
       <c r="M16" s="8">
         <v>754668</v>
@@ -2403,14 +2403,14 @@
       </c>
       <c r="O16" s="4">
         <f t="shared" si="4"/>
-        <v>125402</v>
+        <v>125413</v>
       </c>
       <c r="P16" s="14">
-        <v>749372</v>
+        <v>749383</v>
       </c>
       <c r="Q16" s="5">
         <f t="shared" si="5"/>
-        <v>0.99298234455416157</v>
+        <v>0.99299692050014043</v>
       </c>
       <c r="R16" s="8">
         <v>429537</v>
@@ -2420,14 +2420,14 @@
       </c>
       <c r="T16" s="4">
         <f t="shared" si="6"/>
-        <v>78681</v>
+        <v>78689</v>
       </c>
       <c r="U16" s="14">
-        <v>424931</v>
+        <v>424939</v>
       </c>
       <c r="V16" s="5">
         <f t="shared" si="7"/>
-        <v>0.98927682597773881</v>
+        <v>0.98929545068294467</v>
       </c>
       <c r="W16" s="8">
         <v>433887</v>
@@ -2437,14 +2437,14 @@
       </c>
       <c r="Y16" s="4">
         <f t="shared" si="8"/>
-        <v>76023</v>
+        <v>76032</v>
       </c>
       <c r="Z16" s="14">
-        <v>427149</v>
+        <v>427158</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="9"/>
-        <v>0.98447061101162281</v>
+        <v>0.98449135373956809</v>
       </c>
       <c r="AB16" s="8">
         <v>753330</v>
@@ -2454,14 +2454,14 @@
       </c>
       <c r="AD16" s="4">
         <f t="shared" si="10"/>
-        <v>135918</v>
+        <v>135941</v>
       </c>
       <c r="AE16" s="14">
-        <v>750123</v>
+        <v>750146</v>
       </c>
       <c r="AF16" s="5">
         <f t="shared" si="11"/>
-        <v>0.9957429015172633</v>
+        <v>0.99577343262580809</v>
       </c>
       <c r="AG16" s="8">
         <v>431686</v>
@@ -2471,14 +2471,14 @@
       </c>
       <c r="AI16" s="4">
         <f t="shared" si="12"/>
-        <v>82789</v>
+        <v>82803</v>
       </c>
       <c r="AJ16" s="14">
-        <v>426967</v>
+        <v>426981</v>
       </c>
       <c r="AK16" s="5">
         <f t="shared" si="13"/>
-        <v>0.98906844326663357</v>
+        <v>0.98910087424655879</v>
       </c>
       <c r="AL16" s="8">
         <v>438911</v>
@@ -2488,14 +2488,14 @@
       </c>
       <c r="AN16" s="4">
         <f t="shared" si="14"/>
-        <v>74035</v>
+        <v>74048</v>
       </c>
       <c r="AO16" s="14">
-        <v>430616</v>
+        <v>430629</v>
       </c>
       <c r="AP16" s="5">
         <f t="shared" si="15"/>
-        <v>0.98110095212924719</v>
+        <v>0.98113057089022604</v>
       </c>
       <c r="AQ16" s="8">
         <v>759875</v>
@@ -2505,14 +2505,14 @@
       </c>
       <c r="AS16" s="4">
         <f t="shared" si="16"/>
-        <v>120029</v>
+        <v>120058</v>
       </c>
       <c r="AT16" s="14">
-        <v>756924</v>
+        <v>756953</v>
       </c>
       <c r="AU16" s="5">
         <f t="shared" si="17"/>
-        <v>0.99611646652409935</v>
+        <v>0.99615463069583809</v>
       </c>
       <c r="AV16" s="8">
         <v>437477</v>
@@ -2522,14 +2522,14 @@
       </c>
       <c r="AX16" s="4">
         <f t="shared" si="18"/>
-        <v>69897</v>
+        <v>69915</v>
       </c>
       <c r="AY16" s="14">
-        <v>432374</v>
+        <v>432392</v>
       </c>
       <c r="AZ16" s="5">
         <f t="shared" si="19"/>
-        <v>0.98833538677461896</v>
+        <v>0.98837653179481433</v>
       </c>
       <c r="BA16" s="8">
         <v>445887</v>
@@ -2539,14 +2539,14 @@
       </c>
       <c r="BC16" s="4">
         <f t="shared" si="20"/>
-        <v>70535</v>
+        <v>70549</v>
       </c>
       <c r="BD16" s="14">
-        <v>437200</v>
+        <v>437214</v>
       </c>
       <c r="BE16" s="5">
         <f t="shared" si="21"/>
-        <v>0.98051748537185435</v>
+        <v>0.98054888346150482</v>
       </c>
       <c r="BF16" s="8">
         <v>770088</v>
@@ -2556,14 +2556,14 @@
       </c>
       <c r="BH16" s="4">
         <f t="shared" si="22"/>
-        <v>139436</v>
+        <v>139470</v>
       </c>
       <c r="BI16" s="14">
-        <v>762991</v>
+        <v>763025</v>
       </c>
       <c r="BJ16" s="5">
         <f t="shared" si="23"/>
-        <v>0.99078417012081732</v>
+        <v>0.99082832091916773</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2581,14 +2581,14 @@
       </c>
       <c r="E17" s="4">
         <f t="shared" si="0"/>
-        <v>52710</v>
+        <v>52712</v>
       </c>
       <c r="F17" s="14">
-        <v>303728</v>
+        <v>303730</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="1"/>
-        <v>1.0038139430354227</v>
+        <v>1.0038205529886903</v>
       </c>
       <c r="H17" s="8">
         <v>314962</v>
@@ -2598,14 +2598,14 @@
       </c>
       <c r="J17" s="4">
         <f t="shared" si="2"/>
-        <v>52694</v>
+        <v>52697</v>
       </c>
       <c r="K17" s="14">
-        <v>311321</v>
+        <v>311324</v>
       </c>
       <c r="L17" s="5">
         <f t="shared" si="3"/>
-        <v>0.98843987528654254</v>
+        <v>0.98844940024510897</v>
       </c>
       <c r="M17" s="8">
         <v>695415</v>
@@ -2615,14 +2615,14 @@
       </c>
       <c r="O17" s="4">
         <f t="shared" si="4"/>
-        <v>119323</v>
+        <v>119330</v>
       </c>
       <c r="P17" s="14">
-        <v>689984</v>
+        <v>689991</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="5"/>
-        <v>0.99219027487183908</v>
+        <v>0.99220034080369279</v>
       </c>
       <c r="R17" s="8">
         <v>305324</v>
@@ -2632,14 +2632,14 @@
       </c>
       <c r="T17" s="4">
         <f t="shared" si="6"/>
-        <v>55830</v>
+        <v>55836</v>
       </c>
       <c r="U17" s="14">
-        <v>304498</v>
+        <v>304504</v>
       </c>
       <c r="V17" s="5">
         <f t="shared" si="7"/>
-        <v>0.99729467712986863</v>
+        <v>0.99731432838558387</v>
       </c>
       <c r="W17" s="8">
         <v>316716</v>
@@ -2649,14 +2649,14 @@
       </c>
       <c r="Y17" s="4">
         <f t="shared" si="8"/>
-        <v>55820</v>
+        <v>55824</v>
       </c>
       <c r="Z17" s="14">
-        <v>310532</v>
+        <v>310536</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="9"/>
-        <v>0.98047462079591807</v>
+        <v>0.980487250407305</v>
       </c>
       <c r="AB17" s="8">
         <v>703511</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="AD17" s="4">
         <f t="shared" si="10"/>
-        <v>130826</v>
+        <v>130839</v>
       </c>
       <c r="AE17" s="14">
-        <v>698110</v>
+        <v>698123</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" si="11"/>
-        <v>0.99232279239414878</v>
+        <v>0.99234127113861759</v>
       </c>
       <c r="AG17" s="8">
         <v>311084</v>
@@ -2683,14 +2683,14 @@
       </c>
       <c r="AI17" s="4">
         <f t="shared" si="12"/>
-        <v>63047</v>
+        <v>63052</v>
       </c>
       <c r="AJ17" s="14">
-        <v>310726</v>
+        <v>310731</v>
       </c>
       <c r="AK17" s="5">
         <f t="shared" si="13"/>
-        <v>0.99884918542901591</v>
+        <v>0.99886525825821959</v>
       </c>
       <c r="AL17" s="8">
         <v>323550</v>
@@ -2700,14 +2700,14 @@
       </c>
       <c r="AN17" s="4">
         <f t="shared" si="14"/>
-        <v>52114</v>
+        <v>52122</v>
       </c>
       <c r="AO17" s="14">
-        <v>317185</v>
+        <v>317193</v>
       </c>
       <c r="AP17" s="5">
         <f t="shared" si="15"/>
-        <v>0.98032761551537628</v>
+        <v>0.98035234121464998</v>
       </c>
       <c r="AQ17" s="8">
         <v>714257</v>
@@ -2717,14 +2717,14 @@
       </c>
       <c r="AS17" s="4">
         <f t="shared" si="16"/>
-        <v>112895</v>
+        <v>112913</v>
       </c>
       <c r="AT17" s="14">
-        <v>712843</v>
+        <v>712861</v>
       </c>
       <c r="AU17" s="5">
         <f t="shared" si="17"/>
-        <v>0.99802032041688071</v>
+        <v>0.9980455214299615</v>
       </c>
       <c r="AV17" s="8">
         <v>316308</v>
@@ -2734,14 +2734,14 @@
       </c>
       <c r="AX17" s="4">
         <f t="shared" si="18"/>
-        <v>51116</v>
+        <v>51125</v>
       </c>
       <c r="AY17" s="14">
-        <v>316448</v>
+        <v>316457</v>
       </c>
       <c r="AZ17" s="5">
         <f t="shared" si="19"/>
-        <v>1.0004426065733398</v>
+        <v>1.0004710598530546</v>
       </c>
       <c r="BA17" s="8">
         <v>328067</v>
@@ -2751,14 +2751,14 @@
       </c>
       <c r="BC17" s="4">
         <f t="shared" si="20"/>
-        <v>47175</v>
+        <v>47184</v>
       </c>
       <c r="BD17" s="14">
-        <v>322729</v>
+        <v>322738</v>
       </c>
       <c r="BE17" s="5">
         <f t="shared" si="21"/>
-        <v>0.98372893341908818</v>
+        <v>0.98375636683970047</v>
       </c>
       <c r="BF17" s="8">
         <v>726752</v>
@@ -2768,14 +2768,14 @@
       </c>
       <c r="BH17" s="4">
         <f t="shared" si="22"/>
-        <v>143889</v>
+        <v>143913</v>
       </c>
       <c r="BI17" s="14">
-        <v>723941</v>
+        <v>723965</v>
       </c>
       <c r="BJ17" s="5">
         <f t="shared" si="23"/>
-        <v>0.99613210558760068</v>
+        <v>0.99616512923253053</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2793,14 +2793,14 @@
       </c>
       <c r="E18" s="4">
         <f t="shared" si="0"/>
-        <v>166644</v>
+        <v>166645</v>
       </c>
       <c r="F18" s="14">
-        <v>919275</v>
+        <v>919276</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="1"/>
-        <v>0.99787133807189476</v>
+        <v>0.99787242357007322</v>
       </c>
       <c r="H18" s="8">
         <v>943261</v>
@@ -2810,14 +2810,14 @@
       </c>
       <c r="J18" s="4">
         <f t="shared" si="2"/>
-        <v>163851</v>
+        <v>163854</v>
       </c>
       <c r="K18" s="14">
-        <v>933279</v>
+        <v>933282</v>
       </c>
       <c r="L18" s="5">
         <f t="shared" si="3"/>
-        <v>0.98941756311349671</v>
+        <v>0.98942074356938325</v>
       </c>
       <c r="M18" s="8">
         <v>1440086</v>
@@ -2827,14 +2827,14 @@
       </c>
       <c r="O18" s="4">
         <f t="shared" si="4"/>
-        <v>251765</v>
+        <v>251769</v>
       </c>
       <c r="P18" s="14">
-        <v>1426823</v>
+        <v>1426827</v>
       </c>
       <c r="Q18" s="5">
         <f t="shared" si="5"/>
-        <v>0.99079013336703503</v>
+        <v>0.99079291097892763</v>
       </c>
       <c r="R18" s="8">
         <v>938677</v>
@@ -2844,14 +2844,14 @@
       </c>
       <c r="T18" s="4">
         <f t="shared" si="6"/>
-        <v>170686</v>
+        <v>170693</v>
       </c>
       <c r="U18" s="14">
-        <v>929354</v>
+        <v>929361</v>
       </c>
       <c r="V18" s="5">
         <f t="shared" si="7"/>
-        <v>0.99006793604189725</v>
+        <v>0.99007539334616701</v>
       </c>
       <c r="W18" s="8">
         <v>958009</v>
@@ -2861,14 +2861,14 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="8"/>
-        <v>169090</v>
+        <v>169101</v>
       </c>
       <c r="Z18" s="14">
-        <v>943661</v>
+        <v>943672</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="9"/>
-        <v>0.98502310521091141</v>
+        <v>0.98503458735773886</v>
       </c>
       <c r="AB18" s="8">
         <v>1463397</v>
@@ -2878,14 +2878,14 @@
       </c>
       <c r="AD18" s="4">
         <f t="shared" si="10"/>
-        <v>274221</v>
+        <v>274239</v>
       </c>
       <c r="AE18" s="14">
-        <v>1451213</v>
+        <v>1451231</v>
       </c>
       <c r="AF18" s="5">
         <f t="shared" si="11"/>
-        <v>0.99167416634037109</v>
+        <v>0.99168646648858783</v>
       </c>
       <c r="AG18" s="8">
         <v>959088</v>
@@ -2895,14 +2895,14 @@
       </c>
       <c r="AI18" s="4">
         <f t="shared" si="12"/>
-        <v>195140</v>
+        <v>195157</v>
       </c>
       <c r="AJ18" s="14">
-        <v>951993</v>
+        <v>952010</v>
       </c>
       <c r="AK18" s="5">
         <f t="shared" si="13"/>
-        <v>0.9926023472298684</v>
+        <v>0.99262007240211536</v>
       </c>
       <c r="AL18" s="8">
         <v>980581</v>
@@ -2912,14 +2912,14 @@
       </c>
       <c r="AN18" s="4">
         <f t="shared" si="14"/>
-        <v>166835</v>
+        <v>166854</v>
       </c>
       <c r="AO18" s="14">
-        <v>964377</v>
+        <v>964396</v>
       </c>
       <c r="AP18" s="5">
         <f t="shared" si="15"/>
-        <v>0.98347510302565522</v>
+        <v>0.9834944792933985</v>
       </c>
       <c r="AQ18" s="8">
         <v>1490329</v>
@@ -2929,14 +2929,14 @@
       </c>
       <c r="AS18" s="4">
         <f t="shared" si="16"/>
-        <v>246133</v>
+        <v>246160</v>
       </c>
       <c r="AT18" s="14">
-        <v>1482609</v>
+        <v>1482636</v>
       </c>
       <c r="AU18" s="5">
         <f t="shared" si="17"/>
-        <v>0.99481993573231142</v>
+        <v>0.99483805253739277</v>
       </c>
       <c r="AV18" s="8">
         <v>983291</v>
@@ -2946,14 +2946,14 @@
       </c>
       <c r="AX18" s="4">
         <f t="shared" si="18"/>
-        <v>170161</v>
+        <v>170185</v>
       </c>
       <c r="AY18" s="14">
-        <v>975917</v>
+        <v>975941</v>
       </c>
       <c r="AZ18" s="5">
         <f t="shared" si="19"/>
-        <v>0.99250069409767805</v>
+        <v>0.99252510192811694</v>
       </c>
       <c r="BA18" s="8">
         <v>1002255</v>
@@ -2963,14 +2963,14 @@
       </c>
       <c r="BC18" s="4">
         <f t="shared" si="20"/>
-        <v>160679</v>
+        <v>160704</v>
       </c>
       <c r="BD18" s="14">
-        <v>988280</v>
+        <v>988305</v>
       </c>
       <c r="BE18" s="5">
         <f t="shared" si="21"/>
-        <v>0.9860564427216626</v>
+        <v>0.9860813864735023</v>
       </c>
       <c r="BF18" s="8">
         <v>1522890</v>
@@ -2980,14 +2980,14 @@
       </c>
       <c r="BH18" s="4">
         <f t="shared" si="22"/>
-        <v>329348</v>
+        <v>329387</v>
       </c>
       <c r="BI18" s="14">
-        <v>1509089</v>
+        <v>1509128</v>
       </c>
       <c r="BJ18" s="5">
         <f t="shared" si="23"/>
-        <v>0.9909376251731904</v>
+        <v>0.99096323437674416</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3005,14 +3005,14 @@
       </c>
       <c r="E19" s="4">
         <f t="shared" si="0"/>
-        <v>63743</v>
+        <v>63748</v>
       </c>
       <c r="F19" s="14">
-        <v>271486</v>
+        <v>271491</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="1"/>
-        <v>0.98652228419847743</v>
+        <v>0.9865404531332328</v>
       </c>
       <c r="H19" s="8">
         <v>285702</v>
@@ -3022,14 +3022,14 @@
       </c>
       <c r="J19" s="4">
         <f t="shared" si="2"/>
-        <v>60457</v>
+        <v>60463</v>
       </c>
       <c r="K19" s="14">
-        <v>277219</v>
+        <v>277225</v>
       </c>
       <c r="L19" s="5">
         <f t="shared" si="3"/>
-        <v>0.97030822325359989</v>
+        <v>0.97032922415663869</v>
       </c>
       <c r="M19" s="8">
         <v>479092</v>
@@ -3039,14 +3039,14 @@
       </c>
       <c r="O19" s="4">
         <f t="shared" si="4"/>
-        <v>93787</v>
+        <v>93795</v>
       </c>
       <c r="P19" s="14">
-        <v>468692</v>
+        <v>468700</v>
       </c>
       <c r="Q19" s="5">
         <f t="shared" si="5"/>
-        <v>0.97829226954321924</v>
+        <v>0.97830896779741683</v>
       </c>
       <c r="R19" s="8">
         <v>279649</v>
@@ -3056,14 +3056,14 @@
       </c>
       <c r="T19" s="4">
         <f t="shared" si="6"/>
-        <v>57751</v>
+        <v>57758</v>
       </c>
       <c r="U19" s="14">
-        <v>272795</v>
+        <v>272802</v>
       </c>
       <c r="V19" s="5">
         <f t="shared" si="7"/>
-        <v>0.97549070441875352</v>
+        <v>0.97551573579737461</v>
       </c>
       <c r="W19" s="8">
         <v>287758</v>
@@ -3073,14 +3073,14 @@
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="8"/>
-        <v>59227</v>
+        <v>59236</v>
       </c>
       <c r="Z19" s="14">
-        <v>276647</v>
+        <v>276656</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="9"/>
-        <v>0.96138769382606215</v>
+        <v>0.96141897010682587</v>
       </c>
       <c r="AB19" s="8">
         <v>485015</v>
@@ -3090,14 +3090,14 @@
       </c>
       <c r="AD19" s="4">
         <f t="shared" si="10"/>
-        <v>101792</v>
+        <v>101811</v>
       </c>
       <c r="AE19" s="14">
-        <v>474978</v>
+        <v>474997</v>
       </c>
       <c r="AF19" s="5">
         <f t="shared" si="11"/>
-        <v>0.97930579466614431</v>
+        <v>0.97934496871230792</v>
       </c>
       <c r="AG19" s="8">
         <v>283525</v>
@@ -3107,14 +3107,14 @@
       </c>
       <c r="AI19" s="4">
         <f t="shared" si="12"/>
-        <v>74615</v>
+        <v>74630</v>
       </c>
       <c r="AJ19" s="14">
-        <v>276718</v>
+        <v>276733</v>
       </c>
       <c r="AK19" s="5">
         <f t="shared" si="13"/>
-        <v>0.97599153513799486</v>
+        <v>0.97604444052552686</v>
       </c>
       <c r="AL19" s="8">
         <v>295027</v>
@@ -3124,14 +3124,14 @@
       </c>
       <c r="AN19" s="4">
         <f t="shared" si="14"/>
-        <v>58086</v>
+        <v>58101</v>
       </c>
       <c r="AO19" s="14">
-        <v>282164</v>
+        <v>282179</v>
       </c>
       <c r="AP19" s="5">
         <f t="shared" si="15"/>
-        <v>0.95640060062299381</v>
+        <v>0.95645144342721178</v>
       </c>
       <c r="AQ19" s="8">
         <v>494059</v>
@@ -3141,14 +3141,14 @@
       </c>
       <c r="AS19" s="4">
         <f t="shared" si="16"/>
-        <v>91602</v>
+        <v>91626</v>
       </c>
       <c r="AT19" s="14">
-        <v>486390</v>
+        <v>486414</v>
       </c>
       <c r="AU19" s="5">
         <f t="shared" si="17"/>
-        <v>0.98447756239639395</v>
+        <v>0.98452613959061575</v>
       </c>
       <c r="AV19" s="8">
         <v>287237</v>
@@ -3158,14 +3158,14 @@
       </c>
       <c r="AX19" s="4">
         <f t="shared" si="18"/>
-        <v>56651</v>
+        <v>56668</v>
       </c>
       <c r="AY19" s="14">
-        <v>283401</v>
+        <v>283418</v>
       </c>
       <c r="AZ19" s="5">
         <f t="shared" si="19"/>
-        <v>0.98664517454227696</v>
+        <v>0.98670435911808019</v>
       </c>
       <c r="BA19" s="8">
         <v>298081</v>
@@ -3175,14 +3175,14 @@
       </c>
       <c r="BC19" s="4">
         <f t="shared" si="20"/>
-        <v>55006</v>
+        <v>55023</v>
       </c>
       <c r="BD19" s="14">
-        <v>287517</v>
+        <v>287534</v>
       </c>
       <c r="BE19" s="5">
         <f t="shared" si="21"/>
-        <v>0.96455996859913917</v>
+        <v>0.96461700007716022</v>
       </c>
       <c r="BF19" s="8">
         <v>503654</v>
@@ -3192,14 +3192,14 @@
       </c>
       <c r="BH19" s="4">
         <f t="shared" si="22"/>
-        <v>132341</v>
+        <v>132384</v>
       </c>
       <c r="BI19" s="14">
-        <v>492737</v>
+        <v>492780</v>
       </c>
       <c r="BJ19" s="5">
         <f t="shared" si="23"/>
-        <v>0.97832440524645892</v>
+        <v>0.97840978131812717</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3217,14 +3217,14 @@
       </c>
       <c r="E20" s="4">
         <f t="shared" si="0"/>
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="F20" s="14">
-        <v>5803</v>
+        <v>5804</v>
       </c>
       <c r="G20" s="5">
         <f t="shared" si="1"/>
-        <v>1.0281715095676824</v>
+        <v>1.0283486888731397</v>
       </c>
       <c r="H20" s="8">
         <v>5914</v>
@@ -3234,14 +3234,14 @@
       </c>
       <c r="J20" s="4">
         <f t="shared" si="2"/>
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="K20" s="14">
-        <v>5961</v>
+        <v>5962</v>
       </c>
       <c r="L20" s="5">
         <f t="shared" si="3"/>
-        <v>1.0079472438282042</v>
+        <v>1.0081163341224213</v>
       </c>
       <c r="M20" s="8">
         <v>9037</v>
@@ -3251,14 +3251,14 @@
       </c>
       <c r="O20" s="4">
         <f t="shared" si="4"/>
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="P20" s="14">
-        <v>9277</v>
+        <v>9278</v>
       </c>
       <c r="Q20" s="5">
         <f t="shared" si="5"/>
-        <v>1.0265574858913356</v>
+        <v>1.0266681420825494</v>
       </c>
       <c r="R20" s="8">
         <v>5910</v>
@@ -3268,14 +3268,14 @@
       </c>
       <c r="T20" s="4">
         <f t="shared" si="6"/>
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="U20" s="14">
-        <v>6037</v>
+        <v>6038</v>
       </c>
       <c r="V20" s="5">
         <f t="shared" si="7"/>
-        <v>1.0214890016920475</v>
+        <v>1.0216582064297801</v>
       </c>
       <c r="W20" s="8">
         <v>6115</v>
@@ -3285,14 +3285,14 @@
       </c>
       <c r="Y20" s="4">
         <f t="shared" si="8"/>
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="Z20" s="14">
-        <v>6148</v>
+        <v>6149</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="9"/>
-        <v>1.0053965658217499</v>
+        <v>1.0055600981193786</v>
       </c>
       <c r="AB20" s="8">
         <v>9431</v>
@@ -3302,14 +3302,14 @@
       </c>
       <c r="AD20" s="4">
         <f t="shared" si="10"/>
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="AE20" s="14">
-        <v>9548</v>
+        <v>9549</v>
       </c>
       <c r="AF20" s="5">
         <f t="shared" si="11"/>
-        <v>1.0124058954511717</v>
+        <v>1.0125119287456261</v>
       </c>
       <c r="AG20" s="8">
         <v>6099</v>
@@ -3319,14 +3319,14 @@
       </c>
       <c r="AI20" s="4">
         <f t="shared" si="12"/>
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="AJ20" s="14">
-        <v>6156</v>
+        <v>6157</v>
       </c>
       <c r="AK20" s="5">
         <f t="shared" si="13"/>
-        <v>1.0093457943925233</v>
+        <v>1.0095097556976553</v>
       </c>
       <c r="AL20" s="8">
         <v>6250</v>
@@ -3336,14 +3336,14 @@
       </c>
       <c r="AN20" s="4">
         <f t="shared" si="14"/>
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="AO20" s="14">
-        <v>6245</v>
+        <v>6246</v>
       </c>
       <c r="AP20" s="5">
         <f t="shared" si="15"/>
-        <v>0.99919999999999998</v>
+        <v>0.99936000000000003</v>
       </c>
       <c r="AQ20" s="8">
         <v>9632</v>
@@ -3353,14 +3353,14 @@
       </c>
       <c r="AS20" s="4">
         <f t="shared" si="16"/>
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="AT20" s="14">
-        <v>9731</v>
+        <v>9732</v>
       </c>
       <c r="AU20" s="5">
         <f t="shared" si="17"/>
-        <v>1.0102782392026579</v>
+        <v>1.0103820598006645</v>
       </c>
       <c r="AV20" s="8">
         <v>6297</v>
@@ -3370,14 +3370,14 @@
       </c>
       <c r="AX20" s="4">
         <f t="shared" si="18"/>
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="AY20" s="14">
-        <v>6268</v>
+        <v>6271</v>
       </c>
       <c r="AZ20" s="5">
         <f t="shared" si="19"/>
-        <v>0.99539463236461811</v>
+        <v>0.99587104970620932</v>
       </c>
       <c r="BA20" s="8">
         <v>6366</v>
@@ -3387,14 +3387,14 @@
       </c>
       <c r="BC20" s="4">
         <f t="shared" si="20"/>
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="BD20" s="14">
-        <v>6299</v>
+        <v>6302</v>
       </c>
       <c r="BE20" s="5">
         <f t="shared" si="21"/>
-        <v>0.9894753377316996</v>
+        <v>0.98994659126610118</v>
       </c>
       <c r="BF20" s="8">
         <v>9853</v>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="BH20" s="4">
         <f t="shared" si="22"/>
-        <v>3247</v>
+        <v>3250</v>
       </c>
       <c r="BI20" s="14">
-        <v>9882</v>
+        <v>9885</v>
       </c>
       <c r="BJ20" s="5">
         <f t="shared" si="23"/>
-        <v>1.0029432660103521</v>
+        <v>1.0032477418045265</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3429,14 +3429,14 @@
       </c>
       <c r="E21" s="4">
         <f t="shared" si="0"/>
-        <v>3697</v>
+        <v>3699</v>
       </c>
       <c r="F21" s="14">
-        <v>9831</v>
+        <v>9833</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="1"/>
-        <v>1.0271653954654687</v>
+        <v>1.0273743600459722</v>
       </c>
       <c r="H21" s="8">
         <v>10057</v>
@@ -3446,14 +3446,14 @@
       </c>
       <c r="J21" s="4">
         <f t="shared" si="2"/>
-        <v>3495</v>
+        <v>3497</v>
       </c>
       <c r="K21" s="14">
-        <v>9974</v>
+        <v>9976</v>
       </c>
       <c r="L21" s="5">
         <f t="shared" si="3"/>
-        <v>0.99174704186139007</v>
+        <v>0.99194590832256135</v>
       </c>
       <c r="M21" s="8">
         <v>12982</v>
@@ -3463,14 +3463,14 @@
       </c>
       <c r="O21" s="4">
         <f t="shared" si="4"/>
-        <v>4300</v>
+        <v>4302</v>
       </c>
       <c r="P21" s="14">
-        <v>13241</v>
+        <v>13243</v>
       </c>
       <c r="Q21" s="5">
         <f t="shared" si="5"/>
-        <v>1.0199507009705746</v>
+        <v>1.0201047604375288</v>
       </c>
       <c r="R21" s="8">
         <v>9811</v>
@@ -3480,14 +3480,14 @@
       </c>
       <c r="T21" s="4">
         <f t="shared" si="6"/>
-        <v>3475</v>
+        <v>3477</v>
       </c>
       <c r="U21" s="14">
-        <v>10036</v>
+        <v>10038</v>
       </c>
       <c r="V21" s="5">
         <f t="shared" si="7"/>
-        <v>1.0229334420548364</v>
+        <v>1.0231372948731017</v>
       </c>
       <c r="W21" s="8">
         <v>10152</v>
@@ -3497,14 +3497,14 @@
       </c>
       <c r="Y21" s="4">
         <f t="shared" si="8"/>
-        <v>3294</v>
+        <v>3297</v>
       </c>
       <c r="Z21" s="14">
-        <v>10180</v>
+        <v>10183</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="9"/>
-        <v>1.0027580772261624</v>
+        <v>1.0030535855003939</v>
       </c>
       <c r="AB21" s="8">
         <v>13231</v>
@@ -3514,14 +3514,14 @@
       </c>
       <c r="AD21" s="4">
         <f t="shared" si="10"/>
-        <v>4358</v>
+        <v>4361</v>
       </c>
       <c r="AE21" s="14">
-        <v>13568</v>
+        <v>13571</v>
       </c>
       <c r="AF21" s="5">
         <f t="shared" si="11"/>
-        <v>1.0254704859798958</v>
+        <v>1.0256972262111708</v>
       </c>
       <c r="AG21" s="8">
         <v>10040</v>
@@ -3531,14 +3531,14 @@
       </c>
       <c r="AI21" s="4">
         <f t="shared" si="12"/>
-        <v>3823</v>
+        <v>3826</v>
       </c>
       <c r="AJ21" s="14">
-        <v>10251</v>
+        <v>10254</v>
       </c>
       <c r="AK21" s="5">
         <f t="shared" si="13"/>
-        <v>1.02101593625498</v>
+        <v>1.0213147410358565</v>
       </c>
       <c r="AL21" s="8">
         <v>10211</v>
@@ -3548,14 +3548,14 @@
       </c>
       <c r="AN21" s="4">
         <f t="shared" si="14"/>
-        <v>3455</v>
+        <v>3458</v>
       </c>
       <c r="AO21" s="14">
-        <v>10402</v>
+        <v>10405</v>
       </c>
       <c r="AP21" s="5">
         <f t="shared" si="15"/>
-        <v>1.0187053177945353</v>
+        <v>1.0189991185975908</v>
       </c>
       <c r="AQ21" s="8">
         <v>13473</v>
@@ -3565,14 +3565,14 @@
       </c>
       <c r="AS21" s="4">
         <f t="shared" si="16"/>
-        <v>4292</v>
+        <v>4295</v>
       </c>
       <c r="AT21" s="14">
-        <v>13895</v>
+        <v>13898</v>
       </c>
       <c r="AU21" s="5">
         <f t="shared" si="17"/>
-        <v>1.03132190306539</v>
+        <v>1.0315445706227269</v>
       </c>
       <c r="AV21" s="8">
         <v>10213</v>
@@ -3582,14 +3582,14 @@
       </c>
       <c r="AX21" s="4">
         <f t="shared" si="18"/>
-        <v>3531</v>
+        <v>3535</v>
       </c>
       <c r="AY21" s="14">
-        <v>10514</v>
+        <v>10518</v>
       </c>
       <c r="AZ21" s="5">
         <f t="shared" si="19"/>
-        <v>1.0294722412611377</v>
+        <v>1.0298638989523157</v>
       </c>
       <c r="BA21" s="8">
         <v>10449</v>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="BC21" s="4">
         <f t="shared" si="20"/>
-        <v>3341</v>
+        <v>3346</v>
       </c>
       <c r="BD21" s="14">
-        <v>10639</v>
+        <v>10644</v>
       </c>
       <c r="BE21" s="5">
         <f t="shared" si="21"/>
-        <v>1.0181835582352379</v>
+        <v>1.0186620729256388</v>
       </c>
       <c r="BF21" s="8">
         <v>13925</v>
@@ -3616,14 +3616,14 @@
       </c>
       <c r="BH21" s="4">
         <f t="shared" si="22"/>
-        <v>6501</v>
+        <v>6507</v>
       </c>
       <c r="BI21" s="14">
-        <v>14328</v>
+        <v>14334</v>
       </c>
       <c r="BJ21" s="5">
         <f t="shared" si="23"/>
-        <v>1.0289407540394973</v>
+        <v>1.0293716337522443</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3641,14 +3641,14 @@
       </c>
       <c r="E22" s="4">
         <f t="shared" si="0"/>
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="F22" s="14">
-        <v>6228</v>
+        <v>6229</v>
       </c>
       <c r="G22" s="5">
         <f t="shared" si="1"/>
-        <v>1.0112031173891864</v>
+        <v>1.0113654814093196</v>
       </c>
       <c r="H22" s="8">
         <v>6265</v>
@@ -3658,14 +3658,14 @@
       </c>
       <c r="J22" s="4">
         <f t="shared" si="2"/>
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="K22" s="14">
-        <v>6310</v>
+        <v>6312</v>
       </c>
       <c r="L22" s="5">
         <f t="shared" si="3"/>
-        <v>1.0071827613727056</v>
+        <v>1.0075019952114923</v>
       </c>
       <c r="M22" s="8">
         <v>7537</v>
@@ -3675,14 +3675,14 @@
       </c>
       <c r="O22" s="4">
         <f t="shared" si="4"/>
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="P22" s="14">
-        <v>7600</v>
+        <v>7602</v>
       </c>
       <c r="Q22" s="5">
         <f t="shared" si="5"/>
-        <v>1.008358763433727</v>
+        <v>1.0086241210030515</v>
       </c>
       <c r="R22" s="8">
         <v>6306</v>
@@ -3692,14 +3692,14 @@
       </c>
       <c r="T22" s="4">
         <f t="shared" si="6"/>
-        <v>1778</v>
+        <v>1781</v>
       </c>
       <c r="U22" s="14">
-        <v>6365</v>
+        <v>6368</v>
       </c>
       <c r="V22" s="5">
         <f t="shared" si="7"/>
-        <v>1.0093561687281953</v>
+        <v>1.0098319061211545</v>
       </c>
       <c r="W22" s="8">
         <v>6435</v>
@@ -3709,14 +3709,14 @@
       </c>
       <c r="Y22" s="4">
         <f t="shared" si="8"/>
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="Z22" s="14">
-        <v>6438</v>
+        <v>6441</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="9"/>
-        <v>1.0004662004662004</v>
+        <v>1.000932400932401</v>
       </c>
       <c r="AB22" s="8">
         <v>7668</v>
@@ -3726,14 +3726,14 @@
       </c>
       <c r="AD22" s="4">
         <f t="shared" si="10"/>
-        <v>2051</v>
+        <v>2055</v>
       </c>
       <c r="AE22" s="14">
-        <v>7715</v>
+        <v>7719</v>
       </c>
       <c r="AF22" s="5">
         <f t="shared" si="11"/>
-        <v>1.0061293688054251</v>
+        <v>1.0066510172143974</v>
       </c>
       <c r="AG22" s="8">
         <v>6422</v>
@@ -3743,14 +3743,14 @@
       </c>
       <c r="AI22" s="4">
         <f t="shared" si="12"/>
-        <v>1832</v>
+        <v>1837</v>
       </c>
       <c r="AJ22" s="14">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="AK22" s="5">
         <f t="shared" si="13"/>
-        <v>1.005450015571473</v>
+        <v>1.0062285892245406</v>
       </c>
       <c r="AL22" s="8">
         <v>6508</v>
@@ -3760,14 +3760,14 @@
       </c>
       <c r="AN22" s="4">
         <f t="shared" si="14"/>
-        <v>1635</v>
+        <v>1641</v>
       </c>
       <c r="AO22" s="14">
-        <v>6504</v>
+        <v>6510</v>
       </c>
       <c r="AP22" s="5">
         <f t="shared" si="15"/>
-        <v>0.99938537185003073</v>
+        <v>1.0003073140749847</v>
       </c>
       <c r="AQ22" s="8">
         <v>7781</v>
@@ -3777,14 +3777,14 @@
       </c>
       <c r="AS22" s="4">
         <f t="shared" si="16"/>
-        <v>2101</v>
+        <v>2107</v>
       </c>
       <c r="AT22" s="14">
-        <v>7813</v>
+        <v>7819</v>
       </c>
       <c r="AU22" s="5">
         <f t="shared" si="17"/>
-        <v>1.0041125819303431</v>
+        <v>1.0048836910422825</v>
       </c>
       <c r="AV22" s="8">
         <v>6603</v>
@@ -3794,14 +3794,14 @@
       </c>
       <c r="AX22" s="4">
         <f t="shared" si="18"/>
-        <v>1651</v>
+        <v>1657</v>
       </c>
       <c r="AY22" s="14">
-        <v>6520</v>
+        <v>6526</v>
       </c>
       <c r="AZ22" s="5">
         <f t="shared" si="19"/>
-        <v>0.98742995608056949</v>
+        <v>0.98833863395426325</v>
       </c>
       <c r="BA22" s="8">
         <v>6608</v>
@@ -3811,14 +3811,14 @@
       </c>
       <c r="BC22" s="4">
         <f t="shared" si="20"/>
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="BD22" s="14">
-        <v>6561</v>
+        <v>6566</v>
       </c>
       <c r="BE22" s="5">
         <f t="shared" si="21"/>
-        <v>0.99288740920096852</v>
+        <v>0.99364406779661019</v>
       </c>
       <c r="BF22" s="8">
         <v>7906</v>
@@ -3828,14 +3828,14 @@
       </c>
       <c r="BH22" s="4">
         <f t="shared" si="22"/>
-        <v>2457</v>
+        <v>2463</v>
       </c>
       <c r="BI22" s="14">
-        <v>7955</v>
+        <v>7961</v>
       </c>
       <c r="BJ22" s="5">
         <f t="shared" si="23"/>
-        <v>1.0061978244371363</v>
+        <v>1.006956741715153</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3853,14 +3853,14 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="0"/>
-        <v>5986</v>
+        <v>5987</v>
       </c>
       <c r="F23" s="14">
-        <v>8473</v>
+        <v>8474</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="1"/>
-        <v>0.96284090909090914</v>
+        <v>0.96295454545454551</v>
       </c>
       <c r="H23" s="8">
         <v>8763</v>
@@ -3870,14 +3870,14 @@
       </c>
       <c r="J23" s="4">
         <f t="shared" si="2"/>
-        <v>5150</v>
+        <v>5151</v>
       </c>
       <c r="K23" s="14">
-        <v>8502</v>
+        <v>8503</v>
       </c>
       <c r="L23" s="5">
         <f t="shared" si="3"/>
-        <v>0.97021567956179389</v>
+        <v>0.97032979573205524</v>
       </c>
       <c r="M23" s="8">
         <v>10654</v>
@@ -3887,14 +3887,14 @@
       </c>
       <c r="O23" s="4">
         <f t="shared" si="4"/>
-        <v>5547</v>
+        <v>5548</v>
       </c>
       <c r="P23" s="14">
-        <v>10479</v>
+        <v>10480</v>
       </c>
       <c r="Q23" s="5">
         <f t="shared" si="5"/>
-        <v>0.9835742444152431</v>
+        <v>0.98366810587572739</v>
       </c>
       <c r="R23" s="8">
         <v>8621</v>
@@ -3904,14 +3904,14 @@
       </c>
       <c r="T23" s="4">
         <f t="shared" si="6"/>
-        <v>3752</v>
+        <v>3753</v>
       </c>
       <c r="U23" s="14">
-        <v>8396</v>
+        <v>8397</v>
       </c>
       <c r="V23" s="5">
         <f t="shared" si="7"/>
-        <v>0.97390093956617563</v>
+        <v>0.97401693539032597</v>
       </c>
       <c r="W23" s="8">
         <v>8774</v>
@@ -3921,14 +3921,14 @@
       </c>
       <c r="Y23" s="4">
         <f t="shared" si="8"/>
-        <v>3701</v>
+        <v>3702</v>
       </c>
       <c r="Z23" s="14">
-        <v>8432</v>
+        <v>8433</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="9"/>
-        <v>0.96102119899703675</v>
+        <v>0.96113517209938459</v>
       </c>
       <c r="AB23" s="8">
         <v>10734</v>
@@ -3938,14 +3938,14 @@
       </c>
       <c r="AD23" s="4">
         <f t="shared" si="10"/>
-        <v>3666</v>
+        <v>3667</v>
       </c>
       <c r="AE23" s="14">
-        <v>10554</v>
+        <v>10555</v>
       </c>
       <c r="AF23" s="5">
         <f t="shared" si="11"/>
-        <v>0.98323085522638343</v>
+        <v>0.98332401714179241</v>
       </c>
       <c r="AG23" s="8">
         <v>8589</v>
@@ -3955,14 +3955,14 @@
       </c>
       <c r="AI23" s="4">
         <f t="shared" si="12"/>
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="AJ23" s="14">
-        <v>8443</v>
+        <v>8444</v>
       </c>
       <c r="AK23" s="5">
         <f t="shared" si="13"/>
-        <v>0.98300151356386078</v>
+        <v>0.98311794155314935</v>
       </c>
       <c r="AL23" s="8">
         <v>8660</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="AN23" s="4">
         <f t="shared" si="14"/>
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="AO23" s="14">
-        <v>8506</v>
+        <v>8507</v>
       </c>
       <c r="AP23" s="5">
         <f t="shared" si="15"/>
-        <v>0.98221709006928404</v>
+        <v>0.98233256351039266</v>
       </c>
       <c r="AQ23" s="8">
         <v>10698</v>
@@ -3989,14 +3989,14 @@
       </c>
       <c r="AS23" s="4">
         <f t="shared" si="16"/>
-        <v>3519</v>
+        <v>3521</v>
       </c>
       <c r="AT23" s="14">
-        <v>10738</v>
+        <v>10740</v>
       </c>
       <c r="AU23" s="5">
         <f t="shared" si="17"/>
-        <v>1.003739016638624</v>
+        <v>1.0039259674705552</v>
       </c>
       <c r="AV23" s="8">
         <v>8445</v>
@@ -4006,14 +4006,14 @@
       </c>
       <c r="AX23" s="4">
         <f t="shared" si="18"/>
-        <v>2800</v>
+        <v>2802</v>
       </c>
       <c r="AY23" s="14">
-        <v>8498</v>
+        <v>8500</v>
       </c>
       <c r="AZ23" s="5">
         <f t="shared" si="19"/>
-        <v>1.006275902901125</v>
+        <v>1.0065127294256957</v>
       </c>
       <c r="BA23" s="8">
         <v>8623</v>
@@ -4023,14 +4023,14 @@
       </c>
       <c r="BC23" s="4">
         <f t="shared" si="20"/>
-        <v>2722</v>
+        <v>2724</v>
       </c>
       <c r="BD23" s="14">
-        <v>8545</v>
+        <v>8547</v>
       </c>
       <c r="BE23" s="5">
         <f t="shared" si="21"/>
-        <v>0.99095442421431057</v>
+        <v>0.99118636205496924</v>
       </c>
       <c r="BF23" s="8">
         <v>11023</v>
@@ -4040,14 +4040,14 @@
       </c>
       <c r="BH23" s="4">
         <f t="shared" si="22"/>
-        <v>4237</v>
+        <v>4239</v>
       </c>
       <c r="BI23" s="14">
-        <v>10908</v>
+        <v>10910</v>
       </c>
       <c r="BJ23" s="5">
         <f t="shared" si="23"/>
-        <v>0.98956726843871901</v>
+        <v>0.98974870724848041</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4167,14 +4167,14 @@
       </c>
       <c r="AI24" s="4">
         <f t="shared" si="12"/>
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="AJ24" s="14">
-        <v>5952</v>
+        <v>5953</v>
       </c>
       <c r="AK24" s="5">
         <f t="shared" si="13"/>
-        <v>0.97959183673469385</v>
+        <v>0.97975641869651087</v>
       </c>
       <c r="AL24" s="8">
         <v>6181</v>
@@ -4184,14 +4184,14 @@
       </c>
       <c r="AN24" s="4">
         <f t="shared" si="14"/>
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="AO24" s="14">
-        <v>6012</v>
+        <v>6013</v>
       </c>
       <c r="AP24" s="5">
         <f t="shared" si="15"/>
-        <v>0.97265814593107913</v>
+        <v>0.97281993204983008</v>
       </c>
       <c r="AQ24" s="8">
         <v>6974</v>
@@ -4201,14 +4201,14 @@
       </c>
       <c r="AS24" s="4">
         <f t="shared" si="16"/>
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="AT24" s="14">
-        <v>6901</v>
+        <v>6902</v>
       </c>
       <c r="AU24" s="5">
         <f t="shared" si="17"/>
-        <v>0.98953254946945801</v>
+        <v>0.9896759392027531</v>
       </c>
       <c r="AV24" s="8">
         <v>6124</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="AX24" s="4">
         <f t="shared" si="18"/>
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="AY24" s="14">
-        <v>6045</v>
+        <v>6046</v>
       </c>
       <c r="AZ24" s="5">
         <f t="shared" si="19"/>
-        <v>0.98709993468321355</v>
+        <v>0.98726322664924882</v>
       </c>
       <c r="BA24" s="8">
         <v>6202</v>
@@ -4235,14 +4235,14 @@
       </c>
       <c r="BC24" s="4">
         <f t="shared" si="20"/>
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="BD24" s="14">
-        <v>6136</v>
+        <v>6137</v>
       </c>
       <c r="BE24" s="5">
         <f t="shared" si="21"/>
-        <v>0.98935827152531441</v>
+        <v>0.98951950983553694</v>
       </c>
       <c r="BF24" s="8">
         <v>7084</v>
@@ -4252,14 +4252,14 @@
       </c>
       <c r="BH24" s="4">
         <f t="shared" si="22"/>
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="BI24" s="14">
-        <v>7030</v>
+        <v>7032</v>
       </c>
       <c r="BJ24" s="5">
         <f t="shared" si="23"/>
-        <v>0.99237718802936192</v>
+        <v>0.99265951439864486</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4277,14 +4277,14 @@
       </c>
       <c r="E25" s="4">
         <f t="shared" si="0"/>
-        <v>3667</v>
+        <v>3668</v>
       </c>
       <c r="F25" s="14">
-        <v>18489</v>
+        <v>18490</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="1"/>
-        <v>1.0112119886239335</v>
+        <v>1.0112666812513673</v>
       </c>
       <c r="H25" s="8">
         <v>18682</v>
@@ -4294,14 +4294,14 @@
       </c>
       <c r="J25" s="4">
         <f t="shared" si="2"/>
-        <v>3640</v>
+        <v>3641</v>
       </c>
       <c r="K25" s="14">
-        <v>18850</v>
+        <v>18851</v>
       </c>
       <c r="L25" s="5">
         <f t="shared" si="3"/>
-        <v>1.0089926132105771</v>
+        <v>1.0090461406701638</v>
       </c>
       <c r="M25" s="8">
         <v>25970</v>
@@ -4311,14 +4311,14 @@
       </c>
       <c r="O25" s="4">
         <f t="shared" si="4"/>
-        <v>4733</v>
+        <v>4735</v>
       </c>
       <c r="P25" s="14">
-        <v>26234</v>
+        <v>26236</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" si="5"/>
-        <v>1.010165575664228</v>
+        <v>1.0102425876010781</v>
       </c>
       <c r="R25" s="8">
         <v>18895</v>
@@ -4328,14 +4328,14 @@
       </c>
       <c r="T25" s="4">
         <f t="shared" si="6"/>
-        <v>3739</v>
+        <v>3740</v>
       </c>
       <c r="U25" s="14">
-        <v>19062</v>
+        <v>19063</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" si="7"/>
-        <v>1.0088383170150834</v>
+        <v>1.0088912410690658</v>
       </c>
       <c r="W25" s="8">
         <v>19436</v>
@@ -4345,14 +4345,14 @@
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="8"/>
-        <v>3769</v>
+        <v>3770</v>
       </c>
       <c r="Z25" s="14">
-        <v>19322</v>
+        <v>19323</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="9"/>
-        <v>0.99413459559580164</v>
+        <v>0.9941860465116279</v>
       </c>
       <c r="AB25" s="8">
         <v>26661</v>
@@ -4362,14 +4362,14 @@
       </c>
       <c r="AD25" s="4">
         <f t="shared" si="10"/>
-        <v>5250</v>
+        <v>5251</v>
       </c>
       <c r="AE25" s="14">
-        <v>26847</v>
+        <v>26848</v>
       </c>
       <c r="AF25" s="5">
         <f t="shared" si="11"/>
-        <v>1.0069764825025318</v>
+        <v>1.0070139904729756</v>
       </c>
       <c r="AG25" s="8">
         <v>19440</v>
@@ -4379,14 +4379,14 @@
       </c>
       <c r="AI25" s="4">
         <f t="shared" si="12"/>
-        <v>4240</v>
+        <v>4242</v>
       </c>
       <c r="AJ25" s="14">
-        <v>19518</v>
+        <v>19520</v>
       </c>
       <c r="AK25" s="5">
         <f t="shared" si="13"/>
-        <v>1.0040123456790124</v>
+        <v>1.0041152263374487</v>
       </c>
       <c r="AL25" s="8">
         <v>19709</v>
@@ -4396,14 +4396,14 @@
       </c>
       <c r="AN25" s="4">
         <f t="shared" si="14"/>
-        <v>3701</v>
+        <v>3703</v>
       </c>
       <c r="AO25" s="14">
-        <v>19681</v>
+        <v>19683</v>
       </c>
       <c r="AP25" s="5">
         <f t="shared" si="15"/>
-        <v>0.99857932924044857</v>
+        <v>0.99868080572327367</v>
       </c>
       <c r="AQ25" s="8">
         <v>27081</v>
@@ -4413,14 +4413,14 @@
       </c>
       <c r="AS25" s="4">
         <f t="shared" si="16"/>
-        <v>5086</v>
+        <v>5088</v>
       </c>
       <c r="AT25" s="14">
-        <v>27280</v>
+        <v>27282</v>
       </c>
       <c r="AU25" s="5">
         <f t="shared" si="17"/>
-        <v>1.0073483253941877</v>
+        <v>1.0074221779107122</v>
       </c>
       <c r="AV25" s="8">
         <v>19795</v>
@@ -4430,14 +4430,14 @@
       </c>
       <c r="AX25" s="4">
         <f t="shared" si="18"/>
-        <v>3987</v>
+        <v>3989</v>
       </c>
       <c r="AY25" s="14">
-        <v>19930</v>
+        <v>19932</v>
       </c>
       <c r="AZ25" s="5">
         <f t="shared" si="19"/>
-        <v>1.0068199040161656</v>
+        <v>1.00692093963122</v>
       </c>
       <c r="BA25" s="8">
         <v>20139</v>
@@ -4447,14 +4447,14 @@
       </c>
       <c r="BC25" s="4">
         <f t="shared" si="20"/>
-        <v>3855</v>
+        <v>3858</v>
       </c>
       <c r="BD25" s="14">
-        <v>20129</v>
+        <v>20132</v>
       </c>
       <c r="BE25" s="5">
         <f t="shared" si="21"/>
-        <v>0.99950345101544269</v>
+        <v>0.99965241571080987</v>
       </c>
       <c r="BF25" s="8">
         <v>27639</v>
@@ -4464,14 +4464,14 @@
       </c>
       <c r="BH25" s="4">
         <f t="shared" si="22"/>
-        <v>7530</v>
+        <v>7533</v>
       </c>
       <c r="BI25" s="14">
-        <v>27768</v>
+        <v>27771</v>
       </c>
       <c r="BJ25" s="5">
         <f t="shared" si="23"/>
-        <v>1.00466731792033</v>
+        <v>1.0047758601975469</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="E26" s="4">
         <f t="shared" si="0"/>
-        <v>3466</v>
+        <v>3470</v>
       </c>
       <c r="F26" s="14">
-        <v>13366</v>
+        <v>13370</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="1"/>
-        <v>0.9875138529737717</v>
+        <v>0.98780938308090138</v>
       </c>
       <c r="H26" s="8">
         <v>13884</v>
@@ -4506,14 +4506,14 @@
       </c>
       <c r="J26" s="4">
         <f t="shared" si="2"/>
-        <v>3311</v>
+        <v>3315</v>
       </c>
       <c r="K26" s="14">
-        <v>13939</v>
+        <v>13943</v>
       </c>
       <c r="L26" s="5">
         <f t="shared" si="3"/>
-        <v>1.0039613944108325</v>
+        <v>1.0042494958225294</v>
       </c>
       <c r="M26" s="8">
         <v>25920</v>
@@ -4523,14 +4523,14 @@
       </c>
       <c r="O26" s="4">
         <f t="shared" si="4"/>
-        <v>5145</v>
+        <v>5151</v>
       </c>
       <c r="P26" s="14">
-        <v>26306</v>
+        <v>26312</v>
       </c>
       <c r="Q26" s="5">
         <f t="shared" si="5"/>
-        <v>1.0148919753086421</v>
+        <v>1.0151234567901235</v>
       </c>
       <c r="R26" s="8">
         <v>13869</v>
@@ -4540,14 +4540,14 @@
       </c>
       <c r="T26" s="4">
         <f t="shared" si="6"/>
-        <v>3714</v>
+        <v>3717</v>
       </c>
       <c r="U26" s="14">
-        <v>14175</v>
+        <v>14178</v>
       </c>
       <c r="V26" s="5">
         <f t="shared" si="7"/>
-        <v>1.0220635950681376</v>
+        <v>1.0222799048237075</v>
       </c>
       <c r="W26" s="8">
         <v>14474</v>
@@ -4557,14 +4557,14 @@
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="8"/>
-        <v>3397</v>
+        <v>3401</v>
       </c>
       <c r="Z26" s="14">
-        <v>14442</v>
+        <v>14446</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="9"/>
-        <v>0.99778913914605505</v>
+        <v>0.9980654967527981</v>
       </c>
       <c r="AB26" s="8">
         <v>27035</v>
@@ -4574,14 +4574,14 @@
       </c>
       <c r="AD26" s="4">
         <f t="shared" si="10"/>
-        <v>5647</v>
+        <v>5656</v>
       </c>
       <c r="AE26" s="14">
-        <v>26985</v>
+        <v>26994</v>
       </c>
       <c r="AF26" s="5">
         <f t="shared" si="11"/>
-        <v>0.99815054558905125</v>
+        <v>0.99848344738302197</v>
       </c>
       <c r="AG26" s="8">
         <v>14053</v>
@@ -4591,14 +4591,14 @@
       </c>
       <c r="AI26" s="4">
         <f t="shared" si="12"/>
-        <v>3380</v>
+        <v>3385</v>
       </c>
       <c r="AJ26" s="14">
-        <v>14101</v>
+        <v>14106</v>
       </c>
       <c r="AK26" s="5">
         <f t="shared" si="13"/>
-        <v>1.0034156407884438</v>
+        <v>1.0037714367039066</v>
       </c>
       <c r="AL26" s="8">
         <v>14372</v>
@@ -4608,14 +4608,14 @@
       </c>
       <c r="AN26" s="4">
         <f t="shared" si="14"/>
-        <v>3147</v>
+        <v>3153</v>
       </c>
       <c r="AO26" s="14">
-        <v>14231</v>
+        <v>14237</v>
       </c>
       <c r="AP26" s="5">
         <f t="shared" si="15"/>
-        <v>0.9901892568883941</v>
+        <v>0.99060673531867516</v>
       </c>
       <c r="AQ26" s="8">
         <v>27267</v>
@@ -4625,14 +4625,14 @@
       </c>
       <c r="AS26" s="4">
         <f t="shared" si="16"/>
-        <v>5398</v>
+        <v>5408</v>
       </c>
       <c r="AT26" s="14">
-        <v>27091</v>
+        <v>27101</v>
       </c>
       <c r="AU26" s="5">
         <f t="shared" si="17"/>
-        <v>0.99354531118201495</v>
+        <v>0.9939120548648549</v>
       </c>
       <c r="AV26" s="8">
         <v>14007</v>
@@ -4642,14 +4642,14 @@
       </c>
       <c r="AX26" s="4">
         <f t="shared" si="18"/>
-        <v>3142</v>
+        <v>3148</v>
       </c>
       <c r="AY26" s="14">
-        <v>14026</v>
+        <v>14032</v>
       </c>
       <c r="AZ26" s="5">
         <f t="shared" si="19"/>
-        <v>1.0013564646248305</v>
+        <v>1.0017848218747769</v>
       </c>
       <c r="BA26" s="8">
         <v>14398</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="BC26" s="4">
         <f t="shared" si="20"/>
-        <v>3058</v>
+        <v>3064</v>
       </c>
       <c r="BD26" s="14">
-        <v>14110</v>
+        <v>14116</v>
       </c>
       <c r="BE26" s="5">
         <f t="shared" si="21"/>
-        <v>0.97999722183636617</v>
+        <v>0.98041394638144186</v>
       </c>
       <c r="BF26" s="8">
         <v>27339</v>
@@ -4676,14 +4676,14 @@
       </c>
       <c r="BH26" s="4">
         <f t="shared" si="22"/>
-        <v>6638</v>
+        <v>6650</v>
       </c>
       <c r="BI26" s="14">
-        <v>27114</v>
+        <v>27126</v>
       </c>
       <c r="BJ26" s="5">
         <f t="shared" si="23"/>
-        <v>0.99176999890266648</v>
+        <v>0.99220893229452434</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4701,14 +4701,14 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="0"/>
-        <v>34632</v>
+        <v>34642</v>
       </c>
       <c r="F27" s="14">
-        <v>120709</v>
+        <v>120719</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="1"/>
-        <v>1.0018840988695408</v>
+        <v>1.0019670988197407</v>
       </c>
       <c r="H27" s="8">
         <v>123649</v>
@@ -4718,14 +4718,14 @@
       </c>
       <c r="J27" s="4">
         <f t="shared" si="2"/>
-        <v>32456</v>
+        <v>32467</v>
       </c>
       <c r="K27" s="14">
-        <v>122558</v>
+        <v>122569</v>
       </c>
       <c r="L27" s="5">
         <f t="shared" si="3"/>
-        <v>0.99117663709370885</v>
+        <v>0.99126559858955587</v>
       </c>
       <c r="M27" s="8">
         <v>182121</v>
@@ -4735,14 +4735,14 @@
       </c>
       <c r="O27" s="4">
         <f t="shared" si="4"/>
-        <v>47481</v>
+        <v>47493</v>
       </c>
       <c r="P27" s="14">
-        <v>180972</v>
+        <v>180984</v>
       </c>
       <c r="Q27" s="5">
         <f t="shared" si="5"/>
-        <v>0.99369100762679752</v>
+        <v>0.99375689788656996</v>
       </c>
       <c r="R27" s="8">
         <v>122848</v>
@@ -4752,14 +4752,14 @@
       </c>
       <c r="T27" s="4">
         <f t="shared" si="6"/>
-        <v>33835</v>
+        <v>33847</v>
       </c>
       <c r="U27" s="14">
-        <v>122064</v>
+        <v>122076</v>
       </c>
       <c r="V27" s="5">
         <f t="shared" si="7"/>
-        <v>0.99361812972128161</v>
+        <v>0.99371581140922116</v>
       </c>
       <c r="W27" s="8">
         <v>125846</v>
@@ -4769,14 +4769,14 @@
       </c>
       <c r="Y27" s="4">
         <f t="shared" si="8"/>
-        <v>34904</v>
+        <v>34918</v>
       </c>
       <c r="Z27" s="14">
-        <v>123352</v>
+        <v>123366</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="9"/>
-        <v>0.98018212736201393</v>
+        <v>0.980293374441778</v>
       </c>
       <c r="AB27" s="8">
         <v>184102</v>
@@ -4786,14 +4786,14 @@
       </c>
       <c r="AD27" s="4">
         <f t="shared" si="10"/>
-        <v>50121</v>
+        <v>50136</v>
       </c>
       <c r="AE27" s="14">
-        <v>182703</v>
+        <v>182718</v>
       </c>
       <c r="AF27" s="5">
         <f t="shared" si="11"/>
-        <v>0.99240095164636999</v>
+        <v>0.99248242821913935</v>
       </c>
       <c r="AG27" s="8">
         <v>124176</v>
@@ -4803,14 +4803,14 @@
       </c>
       <c r="AI27" s="4">
         <f t="shared" si="12"/>
-        <v>34597</v>
+        <v>34612</v>
       </c>
       <c r="AJ27" s="14">
-        <v>123214</v>
+        <v>123229</v>
       </c>
       <c r="AK27" s="5">
         <f t="shared" si="13"/>
-        <v>0.99225293132328307</v>
+        <v>0.99237372761242104</v>
       </c>
       <c r="AL27" s="8">
         <v>126536</v>
@@ -4820,14 +4820,14 @@
       </c>
       <c r="AN27" s="4">
         <f t="shared" si="14"/>
-        <v>31867</v>
+        <v>31882</v>
       </c>
       <c r="AO27" s="14">
-        <v>124061</v>
+        <v>124076</v>
       </c>
       <c r="AP27" s="5">
         <f t="shared" si="15"/>
-        <v>0.98044034899159127</v>
+        <v>0.98055889233103621</v>
       </c>
       <c r="AQ27" s="8">
         <v>184835</v>
@@ -4837,14 +4837,14 @@
       </c>
       <c r="AS27" s="4">
         <f t="shared" si="16"/>
-        <v>47474</v>
+        <v>47495</v>
       </c>
       <c r="AT27" s="14">
-        <v>184313</v>
+        <v>184334</v>
       </c>
       <c r="AU27" s="5">
         <f t="shared" si="17"/>
-        <v>0.99717585955040977</v>
+        <v>0.99728947439608295</v>
       </c>
       <c r="AV27" s="8">
         <v>124975</v>
@@ -4854,14 +4854,14 @@
       </c>
       <c r="AX27" s="4">
         <f t="shared" si="18"/>
-        <v>31827</v>
+        <v>31845</v>
       </c>
       <c r="AY27" s="14">
-        <v>124367</v>
+        <v>124385</v>
       </c>
       <c r="AZ27" s="5">
         <f t="shared" si="19"/>
-        <v>0.99513502700540113</v>
+        <v>0.99527905581116227</v>
       </c>
       <c r="BA27" s="8">
         <v>127493</v>
@@ -4871,14 +4871,14 @@
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="20"/>
-        <v>31143</v>
+        <v>31163</v>
       </c>
       <c r="BD27" s="14">
-        <v>125424</v>
+        <v>125444</v>
       </c>
       <c r="BE27" s="5">
         <f t="shared" si="21"/>
-        <v>0.98377165805181466</v>
+        <v>0.98392852940945774</v>
       </c>
       <c r="BF27" s="8">
         <v>187636</v>
@@ -4888,14 +4888,14 @@
       </c>
       <c r="BH27" s="4">
         <f t="shared" si="22"/>
-        <v>63175</v>
+        <v>63208</v>
       </c>
       <c r="BI27" s="14">
-        <v>185728</v>
+        <v>185761</v>
       </c>
       <c r="BJ27" s="5">
         <f t="shared" si="23"/>
-        <v>0.98983137564220081</v>
+        <v>0.99000724807606222</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4947,14 +4947,14 @@
       </c>
       <c r="O28" s="4">
         <f t="shared" si="4"/>
-        <v>104706</v>
+        <v>104708</v>
       </c>
       <c r="P28" s="14">
-        <v>645779</v>
+        <v>645781</v>
       </c>
       <c r="Q28" s="5">
         <f t="shared" si="5"/>
-        <v>0.9921461504307173</v>
+        <v>0.99214922314181642</v>
       </c>
       <c r="R28" s="8">
         <v>389073</v>
@@ -4964,14 +4964,14 @@
       </c>
       <c r="T28" s="4">
         <f t="shared" si="6"/>
-        <v>67532</v>
+        <v>67533</v>
       </c>
       <c r="U28" s="14">
-        <v>386536</v>
+        <v>386537</v>
       </c>
       <c r="V28" s="5">
         <f t="shared" si="7"/>
-        <v>0.99347937276552212</v>
+        <v>0.99348194297728187</v>
       </c>
       <c r="W28" s="8">
         <v>397763</v>
@@ -4998,14 +4998,14 @@
       </c>
       <c r="AD28" s="4">
         <f t="shared" si="10"/>
-        <v>103898</v>
+        <v>103903</v>
       </c>
       <c r="AE28" s="14">
-        <v>656463</v>
+        <v>656468</v>
       </c>
       <c r="AF28" s="5">
         <f t="shared" si="11"/>
-        <v>0.99322481129177942</v>
+        <v>0.99323237626353944</v>
       </c>
       <c r="AG28" s="8">
         <v>397417</v>
@@ -5015,14 +5015,14 @@
       </c>
       <c r="AI28" s="4">
         <f t="shared" si="12"/>
-        <v>68399</v>
+        <v>68401</v>
       </c>
       <c r="AJ28" s="14">
-        <v>394603</v>
+        <v>394605</v>
       </c>
       <c r="AK28" s="5">
         <f t="shared" si="13"/>
-        <v>0.99291927622623088</v>
+        <v>0.9929243087235825</v>
       </c>
       <c r="AL28" s="8">
         <v>405895</v>
@@ -5032,14 +5032,14 @@
       </c>
       <c r="AN28" s="4">
         <f t="shared" si="14"/>
-        <v>61123</v>
+        <v>61126</v>
       </c>
       <c r="AO28" s="14">
-        <v>398918</v>
+        <v>398921</v>
       </c>
       <c r="AP28" s="5">
         <f t="shared" si="15"/>
-        <v>0.98281082545978637</v>
+        <v>0.98281821653383261</v>
       </c>
       <c r="AQ28" s="8">
         <v>670091</v>
@@ -5049,14 +5049,14 @@
       </c>
       <c r="AS28" s="4">
         <f t="shared" si="16"/>
-        <v>96092</v>
+        <v>96105</v>
       </c>
       <c r="AT28" s="14">
-        <v>666164</v>
+        <v>666177</v>
       </c>
       <c r="AU28" s="5">
         <f t="shared" si="17"/>
-        <v>0.99413960193466255</v>
+        <v>0.99415900228476428</v>
       </c>
       <c r="AV28" s="8">
         <v>405395</v>
@@ -5066,14 +5066,14 @@
       </c>
       <c r="AX28" s="4">
         <f t="shared" si="18"/>
-        <v>61000</v>
+        <v>61009</v>
       </c>
       <c r="AY28" s="14">
-        <v>402800</v>
+        <v>402809</v>
       </c>
       <c r="AZ28" s="5">
         <f t="shared" si="19"/>
-        <v>0.99359883570344976</v>
+        <v>0.99362103627326437</v>
       </c>
       <c r="BA28" s="8">
         <v>412255</v>
@@ -5083,14 +5083,14 @@
       </c>
       <c r="BC28" s="4">
         <f t="shared" si="20"/>
-        <v>59420</v>
+        <v>59434</v>
       </c>
       <c r="BD28" s="14">
-        <v>406905</v>
+        <v>406919</v>
       </c>
       <c r="BE28" s="5">
         <f t="shared" si="21"/>
-        <v>0.98702259523838398</v>
+        <v>0.98705655480224619</v>
       </c>
       <c r="BF28" s="8">
         <v>680839</v>
@@ -5100,14 +5100,14 @@
       </c>
       <c r="BH28" s="4">
         <f t="shared" si="22"/>
-        <v>127439</v>
+        <v>127470</v>
       </c>
       <c r="BI28" s="14">
-        <v>676348</v>
+        <v>676379</v>
       </c>
       <c r="BJ28" s="5">
         <f t="shared" si="23"/>
-        <v>0.99340372687228551</v>
+        <v>0.99344925892905667</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5125,14 +5125,14 @@
       </c>
       <c r="E29" s="4">
         <f t="shared" si="0"/>
-        <v>24828</v>
+        <v>24830</v>
       </c>
       <c r="F29" s="14">
-        <v>126968</v>
+        <v>126970</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="1"/>
-        <v>0.99538245647044066</v>
+        <v>0.99539813573539671</v>
       </c>
       <c r="H29" s="8">
         <v>129829</v>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="J29" s="4">
         <f t="shared" si="2"/>
-        <v>23859</v>
+        <v>23861</v>
       </c>
       <c r="K29" s="14">
-        <v>128370</v>
+        <v>128372</v>
       </c>
       <c r="L29" s="5">
         <f t="shared" si="3"/>
-        <v>0.98876214097004522</v>
+        <v>0.98877754584877031</v>
       </c>
       <c r="M29" s="8">
         <v>176637</v>
@@ -5159,14 +5159,14 @@
       </c>
       <c r="O29" s="4">
         <f t="shared" si="4"/>
-        <v>30954</v>
+        <v>30958</v>
       </c>
       <c r="P29" s="14">
-        <v>174219</v>
+        <v>174223</v>
       </c>
       <c r="Q29" s="5">
         <f t="shared" si="5"/>
-        <v>0.98631090881298933</v>
+        <v>0.98633355412512669</v>
       </c>
       <c r="R29" s="8">
         <v>129740</v>
@@ -5176,14 +5176,14 @@
       </c>
       <c r="T29" s="4">
         <f t="shared" si="6"/>
-        <v>24247</v>
+        <v>24250</v>
       </c>
       <c r="U29" s="14">
-        <v>128542</v>
+        <v>128545</v>
       </c>
       <c r="V29" s="5">
         <f t="shared" si="7"/>
-        <v>0.99076614767997528</v>
+        <v>0.99078927084939106</v>
       </c>
       <c r="W29" s="8">
         <v>131766</v>
@@ -5193,14 +5193,14 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="8"/>
-        <v>23817</v>
+        <v>23820</v>
       </c>
       <c r="Z29" s="14">
-        <v>129579</v>
+        <v>129582</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="9"/>
-        <v>0.98340239515504757</v>
+        <v>0.98342516278857972</v>
       </c>
       <c r="AB29" s="8">
         <v>178083</v>
@@ -5210,14 +5210,14 @@
       </c>
       <c r="AD29" s="4">
         <f t="shared" si="10"/>
-        <v>32807</v>
+        <v>32814</v>
       </c>
       <c r="AE29" s="14">
-        <v>176361</v>
+        <v>176368</v>
       </c>
       <c r="AF29" s="5">
         <f t="shared" si="11"/>
-        <v>0.99033035157763516</v>
+        <v>0.99036965909154717</v>
       </c>
       <c r="AG29" s="8">
         <v>131984</v>
@@ -5227,14 +5227,14 @@
       </c>
       <c r="AI29" s="4">
         <f t="shared" si="12"/>
-        <v>28870</v>
+        <v>28874</v>
       </c>
       <c r="AJ29" s="14">
-        <v>130689</v>
+        <v>130693</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="13"/>
-        <v>0.99018820463086432</v>
+        <v>0.99021851133470729</v>
       </c>
       <c r="AL29" s="8">
         <v>133676</v>
@@ -5244,14 +5244,14 @@
       </c>
       <c r="AN29" s="4">
         <f t="shared" si="14"/>
-        <v>23045</v>
+        <v>23049</v>
       </c>
       <c r="AO29" s="14">
-        <v>131837</v>
+        <v>131841</v>
       </c>
       <c r="AP29" s="5">
         <f t="shared" si="15"/>
-        <v>0.98624285586043869</v>
+        <v>0.98627277895807774</v>
       </c>
       <c r="AQ29" s="8">
         <v>179800</v>
@@ -5261,14 +5261,14 @@
       </c>
       <c r="AS29" s="4">
         <f t="shared" si="16"/>
-        <v>29851</v>
+        <v>29860</v>
       </c>
       <c r="AT29" s="14">
-        <v>178981</v>
+        <v>178990</v>
       </c>
       <c r="AU29" s="5">
         <f t="shared" si="17"/>
-        <v>0.99544493882091212</v>
+        <v>0.99549499443826472</v>
       </c>
       <c r="AV29" s="8">
         <v>134089</v>
@@ -5278,14 +5278,14 @@
       </c>
       <c r="AX29" s="4">
         <f t="shared" si="18"/>
-        <v>22672</v>
+        <v>22678</v>
       </c>
       <c r="AY29" s="14">
-        <v>133164</v>
+        <v>133170</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="19"/>
-        <v>0.99310159670069875</v>
+        <v>0.993146343100478</v>
       </c>
       <c r="BA29" s="8">
         <v>136058</v>
@@ -5295,14 +5295,14 @@
       </c>
       <c r="BC29" s="4">
         <f t="shared" si="20"/>
-        <v>23015</v>
+        <v>23022</v>
       </c>
       <c r="BD29" s="14">
-        <v>134478</v>
+        <v>134485</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="21"/>
-        <v>0.98838730541386766</v>
+        <v>0.9884387540607682</v>
       </c>
       <c r="BF29" s="8">
         <v>182623</v>
@@ -5312,14 +5312,14 @@
       </c>
       <c r="BH29" s="4">
         <f t="shared" si="22"/>
-        <v>41948</v>
+        <v>41958</v>
       </c>
       <c r="BI29" s="14">
-        <v>181425</v>
+        <v>181435</v>
       </c>
       <c r="BJ29" s="5">
         <f t="shared" si="23"/>
-        <v>0.99344003767323941</v>
+        <v>0.99349479528865481</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5422,14 +5422,14 @@
       </c>
       <c r="AD30" s="4">
         <f t="shared" si="10"/>
-        <v>62877</v>
+        <v>62879</v>
       </c>
       <c r="AE30" s="14">
-        <v>290515</v>
+        <v>290517</v>
       </c>
       <c r="AF30" s="5">
         <f t="shared" si="11"/>
-        <v>0.99048096363196236</v>
+        <v>0.99048778242592228</v>
       </c>
       <c r="AG30" s="8">
         <v>172053</v>
@@ -5439,14 +5439,14 @@
       </c>
       <c r="AI30" s="4">
         <f t="shared" si="12"/>
-        <v>37802</v>
+        <v>37803</v>
       </c>
       <c r="AJ30" s="14">
-        <v>170987</v>
+        <v>170988</v>
       </c>
       <c r="AK30" s="5">
         <f t="shared" si="13"/>
-        <v>0.99380423474162027</v>
+        <v>0.99381004690415164</v>
       </c>
       <c r="AL30" s="8">
         <v>176835</v>
@@ -5456,14 +5456,14 @@
       </c>
       <c r="AN30" s="4">
         <f t="shared" si="14"/>
-        <v>36124</v>
+        <v>36127</v>
       </c>
       <c r="AO30" s="14">
-        <v>173668</v>
+        <v>173671</v>
       </c>
       <c r="AP30" s="5">
         <f t="shared" si="15"/>
-        <v>0.98209064947549973</v>
+        <v>0.98210761444284222</v>
       </c>
       <c r="AQ30" s="8">
         <v>297651</v>
@@ -5473,14 +5473,14 @@
       </c>
       <c r="AS30" s="4">
         <f t="shared" si="16"/>
-        <v>57676</v>
+        <v>57681</v>
       </c>
       <c r="AT30" s="14">
-        <v>296267</v>
+        <v>296272</v>
       </c>
       <c r="AU30" s="5">
         <f t="shared" si="17"/>
-        <v>0.9953502591961727</v>
+        <v>0.99536705739271836</v>
       </c>
       <c r="AV30" s="8">
         <v>175428</v>
@@ -5490,14 +5490,14 @@
       </c>
       <c r="AX30" s="4">
         <f t="shared" si="18"/>
-        <v>36238</v>
+        <v>36244</v>
       </c>
       <c r="AY30" s="14">
-        <v>174384</v>
+        <v>174390</v>
       </c>
       <c r="AZ30" s="5">
         <f t="shared" si="19"/>
-        <v>0.99404884054996923</v>
+        <v>0.99408304261577396</v>
       </c>
       <c r="BA30" s="8">
         <v>179593</v>
@@ -5507,14 +5507,14 @@
       </c>
       <c r="BC30" s="4">
         <f t="shared" si="20"/>
-        <v>36023</v>
+        <v>36028</v>
       </c>
       <c r="BD30" s="14">
-        <v>176251</v>
+        <v>176256</v>
       </c>
       <c r="BE30" s="5">
         <f t="shared" si="21"/>
-        <v>0.98139125689754059</v>
+        <v>0.98141909762629942</v>
       </c>
       <c r="BF30" s="8">
         <v>302258</v>
@@ -5524,14 +5524,14 @@
       </c>
       <c r="BH30" s="4">
         <f t="shared" si="22"/>
-        <v>72858</v>
+        <v>72872</v>
       </c>
       <c r="BI30" s="14">
-        <v>299477</v>
+        <v>299491</v>
       </c>
       <c r="BJ30" s="5">
         <f t="shared" si="23"/>
-        <v>0.99079925097102473</v>
+        <v>0.99084556901719723</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5549,14 +5549,14 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="0"/>
-        <v>21218</v>
+        <v>21221</v>
       </c>
       <c r="F31" s="14">
-        <v>74598</v>
+        <v>74601</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="1"/>
-        <v>1.0011810495235538</v>
+        <v>1.0012213125754932</v>
       </c>
       <c r="H31" s="8">
         <v>76671</v>
@@ -5566,14 +5566,14 @@
       </c>
       <c r="J31" s="4">
         <f t="shared" si="2"/>
-        <v>20127</v>
+        <v>20130</v>
       </c>
       <c r="K31" s="14">
-        <v>75773</v>
+        <v>75776</v>
       </c>
       <c r="L31" s="5">
         <f t="shared" si="3"/>
-        <v>0.98828761852590941</v>
+        <v>0.98832674674909682</v>
       </c>
       <c r="M31" s="8">
         <v>133745</v>
@@ -5583,14 +5583,14 @@
       </c>
       <c r="O31" s="4">
         <f t="shared" si="4"/>
-        <v>35676</v>
+        <v>35678</v>
       </c>
       <c r="P31" s="14">
-        <v>133543</v>
+        <v>133545</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" si="5"/>
-        <v>0.99848966316497811</v>
+        <v>0.9985046169950279</v>
       </c>
       <c r="R31" s="8">
         <v>74974</v>
@@ -5600,14 +5600,14 @@
       </c>
       <c r="T31" s="4">
         <f t="shared" si="6"/>
-        <v>20618</v>
+        <v>20621</v>
       </c>
       <c r="U31" s="14">
-        <v>75033</v>
+        <v>75036</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" si="7"/>
-        <v>1.0007869394723503</v>
+        <v>1.0008269533438259</v>
       </c>
       <c r="W31" s="8">
         <v>77586</v>
@@ -5617,14 +5617,14 @@
       </c>
       <c r="Y31" s="4">
         <f t="shared" si="8"/>
-        <v>21081</v>
+        <v>21083</v>
       </c>
       <c r="Z31" s="14">
-        <v>76090</v>
+        <v>76092</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="9"/>
-        <v>0.98071817080401102</v>
+        <v>0.98074394865052972</v>
       </c>
       <c r="AB31" s="8">
         <v>135116</v>
@@ -5634,14 +5634,14 @@
       </c>
       <c r="AD31" s="4">
         <f t="shared" si="10"/>
-        <v>37196</v>
+        <v>37198</v>
       </c>
       <c r="AE31" s="14">
-        <v>135151</v>
+        <v>135153</v>
       </c>
       <c r="AF31" s="5">
         <f t="shared" si="11"/>
-        <v>1.0002590366795938</v>
+        <v>1.0002738387755705</v>
       </c>
       <c r="AG31" s="8">
         <v>76230</v>
@@ -5651,14 +5651,14 @@
       </c>
       <c r="AI31" s="4">
         <f t="shared" si="12"/>
-        <v>22399</v>
+        <v>22402</v>
       </c>
       <c r="AJ31" s="14">
-        <v>75998</v>
+        <v>76001</v>
       </c>
       <c r="AK31" s="5">
         <f t="shared" si="13"/>
-        <v>0.99695657877476063</v>
+        <v>0.99699593335956971</v>
       </c>
       <c r="AL31" s="8">
         <v>77611</v>
@@ -5668,14 +5668,14 @@
       </c>
       <c r="AN31" s="4">
         <f t="shared" si="14"/>
-        <v>18529</v>
+        <v>18531</v>
       </c>
       <c r="AO31" s="14">
-        <v>76843</v>
+        <v>76845</v>
       </c>
       <c r="AP31" s="5">
         <f t="shared" si="15"/>
-        <v>0.99010449549677237</v>
+        <v>0.99013026503974955</v>
       </c>
       <c r="AQ31" s="8">
         <v>136879</v>
@@ -5685,14 +5685,14 @@
       </c>
       <c r="AS31" s="4">
         <f t="shared" si="16"/>
-        <v>34724</v>
+        <v>34726</v>
       </c>
       <c r="AT31" s="14">
-        <v>137476</v>
+        <v>137478</v>
       </c>
       <c r="AU31" s="5">
         <f t="shared" si="17"/>
-        <v>1.0043615163757771</v>
+        <v>1.0043761278209222</v>
       </c>
       <c r="AV31" s="8">
         <v>76719</v>
@@ -5702,14 +5702,14 @@
       </c>
       <c r="AX31" s="4">
         <f t="shared" si="18"/>
-        <v>18047</v>
+        <v>18049</v>
       </c>
       <c r="AY31" s="14">
-        <v>76908</v>
+        <v>76910</v>
       </c>
       <c r="AZ31" s="5">
         <f t="shared" si="19"/>
-        <v>1.0024635357603722</v>
+        <v>1.0024896049218577</v>
       </c>
       <c r="BA31" s="8">
         <v>78720</v>
@@ -5719,14 +5719,14 @@
       </c>
       <c r="BC31" s="4">
         <f t="shared" si="20"/>
-        <v>18510</v>
+        <v>18512</v>
       </c>
       <c r="BD31" s="14">
-        <v>78334</v>
+        <v>78336</v>
       </c>
       <c r="BE31" s="5">
         <f t="shared" si="21"/>
-        <v>0.99509654471544717</v>
+        <v>0.99512195121951219</v>
       </c>
       <c r="BF31" s="8">
         <v>140181</v>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="BH31" s="4">
         <f t="shared" si="22"/>
-        <v>48223</v>
+        <v>48226</v>
       </c>
       <c r="BI31" s="14">
-        <v>140212</v>
+        <v>140215</v>
       </c>
       <c r="BJ31" s="5">
         <f t="shared" si="23"/>
-        <v>1.0002211426655538</v>
+        <v>1.0002425435686719</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5761,14 +5761,14 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="0"/>
-        <v>45723</v>
+        <v>45725</v>
       </c>
       <c r="F32" s="14">
-        <v>203716</v>
+        <v>203718</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="1"/>
-        <v>0.99999018250719129</v>
+        <v>1</v>
       </c>
       <c r="H32" s="8">
         <v>210874</v>
@@ -5778,14 +5778,14 @@
       </c>
       <c r="J32" s="4">
         <f t="shared" si="2"/>
-        <v>42720</v>
+        <v>42722</v>
       </c>
       <c r="K32" s="14">
-        <v>208092</v>
+        <v>208094</v>
       </c>
       <c r="L32" s="5">
         <f t="shared" si="3"/>
-        <v>0.9868072877642573</v>
+        <v>0.98681677210087537</v>
       </c>
       <c r="M32" s="8">
         <v>441035</v>
@@ -5795,14 +5795,14 @@
       </c>
       <c r="O32" s="4">
         <f t="shared" si="4"/>
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="P32" s="14">
-        <v>438322</v>
+        <v>438325</v>
       </c>
       <c r="Q32" s="5">
         <f t="shared" si="5"/>
-        <v>0.99384856077182082</v>
+        <v>0.99385536295305366</v>
       </c>
       <c r="R32" s="8">
         <v>206418</v>
@@ -5812,14 +5812,14 @@
       </c>
       <c r="T32" s="4">
         <f t="shared" si="6"/>
-        <v>44062</v>
+        <v>44064</v>
       </c>
       <c r="U32" s="14">
-        <v>205103</v>
+        <v>205105</v>
       </c>
       <c r="V32" s="5">
         <f t="shared" si="7"/>
-        <v>0.99362943154182293</v>
+        <v>0.9936391206193258</v>
       </c>
       <c r="W32" s="8">
         <v>212709</v>
@@ -5829,14 +5829,14 @@
       </c>
       <c r="Y32" s="4">
         <f t="shared" si="8"/>
-        <v>45960</v>
+        <v>45962</v>
       </c>
       <c r="Z32" s="14">
-        <v>209147</v>
+        <v>209149</v>
       </c>
       <c r="AA32" s="5">
         <f t="shared" si="9"/>
-        <v>0.98325411712715494</v>
+        <v>0.98326351964420877</v>
       </c>
       <c r="AB32" s="8">
         <v>446806</v>
@@ -5846,14 +5846,14 @@
       </c>
       <c r="AD32" s="4">
         <f t="shared" si="10"/>
-        <v>97540</v>
+        <v>97546</v>
       </c>
       <c r="AE32" s="14">
-        <v>444964</v>
+        <v>444970</v>
       </c>
       <c r="AF32" s="5">
         <f t="shared" si="11"/>
-        <v>0.99587740540637326</v>
+        <v>0.99589083405325807</v>
       </c>
       <c r="AG32" s="8">
         <v>210129</v>
@@ -5863,14 +5863,14 @@
       </c>
       <c r="AI32" s="4">
         <f t="shared" si="12"/>
-        <v>49148</v>
+        <v>49149</v>
       </c>
       <c r="AJ32" s="14">
-        <v>209502</v>
+        <v>209503</v>
       </c>
       <c r="AK32" s="5">
         <f t="shared" si="13"/>
-        <v>0.99701611866995987</v>
+        <v>0.9970208776513475</v>
       </c>
       <c r="AL32" s="8">
         <v>217332</v>
@@ -5880,14 +5880,14 @@
       </c>
       <c r="AN32" s="4">
         <f t="shared" si="14"/>
-        <v>40356</v>
+        <v>40358</v>
       </c>
       <c r="AO32" s="14">
-        <v>212888</v>
+        <v>212890</v>
       </c>
       <c r="AP32" s="5">
         <f t="shared" si="15"/>
-        <v>0.97955202179154477</v>
+        <v>0.97956122430198955</v>
       </c>
       <c r="AQ32" s="8">
         <v>453805</v>
@@ -5897,14 +5897,14 @@
       </c>
       <c r="AS32" s="4">
         <f t="shared" si="16"/>
-        <v>93305</v>
+        <v>93316</v>
       </c>
       <c r="AT32" s="14">
-        <v>452824</v>
+        <v>452835</v>
       </c>
       <c r="AU32" s="5">
         <f t="shared" si="17"/>
-        <v>0.99783827855576734</v>
+        <v>0.99786251804189019</v>
       </c>
       <c r="AV32" s="8">
         <v>213428</v>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="AX32" s="4">
         <f t="shared" si="18"/>
-        <v>40182</v>
+        <v>40186</v>
       </c>
       <c r="AY32" s="14">
-        <v>213407</v>
+        <v>213411</v>
       </c>
       <c r="AZ32" s="5">
         <f t="shared" si="19"/>
-        <v>0.99990160616226553</v>
+        <v>0.99992034784564354</v>
       </c>
       <c r="BA32" s="8">
         <v>220509</v>
@@ -5931,14 +5931,14 @@
       </c>
       <c r="BC32" s="4">
         <f t="shared" si="20"/>
-        <v>39361</v>
+        <v>39364</v>
       </c>
       <c r="BD32" s="14">
-        <v>217603</v>
+        <v>217606</v>
       </c>
       <c r="BE32" s="5">
         <f t="shared" si="21"/>
-        <v>0.98682139958006254</v>
+        <v>0.98683500446693784</v>
       </c>
       <c r="BF32" s="8">
         <v>463937</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="BH32" s="4">
         <f t="shared" si="22"/>
-        <v>127821</v>
+        <v>127829</v>
       </c>
       <c r="BI32" s="14">
-        <v>461023</v>
+        <v>461031</v>
       </c>
       <c r="BJ32" s="5">
         <f t="shared" si="23"/>
-        <v>0.99371897477459226</v>
+        <v>0.99373621849518357</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5973,14 +5973,14 @@
       </c>
       <c r="E33" s="4">
         <f t="shared" si="0"/>
-        <v>74092</v>
+        <v>74095</v>
       </c>
       <c r="F33" s="14">
-        <v>623264</v>
+        <v>623267</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="1"/>
-        <v>1.003653813637791</v>
+        <v>1.0036586445945619</v>
       </c>
       <c r="H33" s="8">
         <v>630476</v>
@@ -5990,14 +5990,14 @@
       </c>
       <c r="J33" s="4">
         <f t="shared" si="2"/>
-        <v>78137</v>
+        <v>78139</v>
       </c>
       <c r="K33" s="14">
-        <v>630449</v>
+        <v>630451</v>
       </c>
       <c r="L33" s="5">
         <f t="shared" si="3"/>
-        <v>0.99995717521364813</v>
+        <v>0.99996034742004458</v>
       </c>
       <c r="M33" s="8">
         <v>1032030</v>
@@ -6007,14 +6007,14 @@
       </c>
       <c r="O33" s="4">
         <f t="shared" si="4"/>
-        <v>130784</v>
+        <v>130787</v>
       </c>
       <c r="P33" s="14">
-        <v>1032145</v>
+        <v>1032148</v>
       </c>
       <c r="Q33" s="5">
         <f t="shared" si="5"/>
-        <v>1.0001114308692576</v>
+        <v>1.0001143377614992</v>
       </c>
       <c r="R33" s="8">
         <v>629419</v>
@@ -6024,14 +6024,14 @@
       </c>
       <c r="T33" s="4">
         <f t="shared" si="6"/>
-        <v>79470</v>
+        <v>79472</v>
       </c>
       <c r="U33" s="14">
-        <v>629964</v>
+        <v>629966</v>
       </c>
       <c r="V33" s="5">
         <f t="shared" si="7"/>
-        <v>1.0008658778969177</v>
+        <v>1.0008690554304842</v>
       </c>
       <c r="W33" s="8">
         <v>637378</v>
@@ -6041,14 +6041,14 @@
       </c>
       <c r="Y33" s="4">
         <f t="shared" si="8"/>
-        <v>80055</v>
+        <v>80056</v>
       </c>
       <c r="Z33" s="14">
-        <v>635164</v>
+        <v>635165</v>
       </c>
       <c r="AA33" s="5">
         <f t="shared" si="9"/>
-        <v>0.99652639407070842</v>
+        <v>0.99652796299840907</v>
       </c>
       <c r="AB33" s="8">
         <v>1041984</v>
@@ -6058,14 +6058,14 @@
       </c>
       <c r="AD33" s="4">
         <f t="shared" si="10"/>
-        <v>142394</v>
+        <v>142397</v>
       </c>
       <c r="AE33" s="14">
-        <v>1042249</v>
+        <v>1042252</v>
       </c>
       <c r="AF33" s="5">
         <f t="shared" si="11"/>
-        <v>1.0002543225231866</v>
+        <v>1.0002572016460904</v>
       </c>
       <c r="AG33" s="8">
         <v>638215</v>
@@ -6092,14 +6092,14 @@
       </c>
       <c r="AN33" s="4">
         <f t="shared" si="14"/>
-        <v>75268</v>
+        <v>75269</v>
       </c>
       <c r="AO33" s="14">
-        <v>642421</v>
+        <v>642422</v>
       </c>
       <c r="AP33" s="5">
         <f t="shared" si="15"/>
-        <v>0.99551074044114685</v>
+        <v>0.99551229006474329</v>
       </c>
       <c r="AQ33" s="8">
         <v>1053133</v>
@@ -6109,14 +6109,14 @@
       </c>
       <c r="AS33" s="4">
         <f t="shared" si="16"/>
-        <v>135442</v>
+        <v>135445</v>
       </c>
       <c r="AT33" s="14">
-        <v>1054028</v>
+        <v>1054031</v>
       </c>
       <c r="AU33" s="5">
         <f t="shared" si="17"/>
-        <v>1.0008498451762502</v>
+        <v>1.0008526938192992</v>
       </c>
       <c r="AV33" s="8">
         <v>647979</v>
@@ -6126,14 +6126,14 @@
       </c>
       <c r="AX33" s="4">
         <f t="shared" si="18"/>
-        <v>69703</v>
+        <v>69705</v>
       </c>
       <c r="AY33" s="14">
-        <v>649950</v>
+        <v>649952</v>
       </c>
       <c r="AZ33" s="5">
         <f t="shared" si="19"/>
-        <v>1.0030417652423922</v>
+        <v>1.0030448517621713</v>
       </c>
       <c r="BA33" s="8">
         <v>657743</v>
@@ -6143,14 +6143,14 @@
       </c>
       <c r="BC33" s="4">
         <f t="shared" si="20"/>
-        <v>65962</v>
+        <v>65964</v>
       </c>
       <c r="BD33" s="14">
-        <v>658029</v>
+        <v>658031</v>
       </c>
       <c r="BE33" s="5">
         <f t="shared" si="21"/>
-        <v>1.0004348202869511</v>
+        <v>1.0004378609882583</v>
       </c>
       <c r="BF33" s="8">
         <v>1071541</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="BH33" s="4">
         <f t="shared" si="22"/>
-        <v>153845</v>
+        <v>153847</v>
       </c>
       <c r="BI33" s="14">
-        <v>1071089</v>
+        <v>1071091</v>
       </c>
       <c r="BJ33" s="5">
         <f t="shared" si="23"/>
-        <v>0.9995781775965642</v>
+        <v>0.99958004406737588</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6585,14 +6585,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="0"/>
-        <v>175070</v>
+        <v>175078</v>
       </c>
       <c r="F36" s="14">
-        <v>834248</v>
+        <v>834256</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="24"/>
-        <v>0.99786014255349942</v>
+        <v>0.99786971150798354</v>
       </c>
       <c r="H36" s="8">
         <v>854298</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="J36" s="4">
         <f t="shared" si="25"/>
-        <v>170055</v>
+        <v>170063</v>
       </c>
       <c r="K36" s="14">
-        <v>844060</v>
+        <v>844068</v>
       </c>
       <c r="L36" s="5">
         <f t="shared" si="26"/>
-        <v>0.98801589141025736</v>
+        <v>0.98802525582408007</v>
       </c>
       <c r="M36" s="8">
         <v>1510524</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="O36" s="4">
         <f t="shared" si="27"/>
-        <v>313998</v>
+        <v>314006</v>
       </c>
       <c r="P36" s="14">
-        <v>1500996</v>
+        <v>1501004</v>
       </c>
       <c r="Q36" s="5">
         <f t="shared" si="28"/>
-        <v>0.99369225513795212</v>
+        <v>0.99369755131331905</v>
       </c>
       <c r="R36" s="8">
         <v>845008</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="T36" s="4">
         <f t="shared" si="29"/>
-        <v>178624</v>
+        <v>178634</v>
       </c>
       <c r="U36" s="14">
-        <v>840689</v>
+        <v>840699</v>
       </c>
       <c r="V36" s="5">
         <f t="shared" si="30"/>
-        <v>0.99488880578645411</v>
+        <v>0.99490063999394085</v>
       </c>
       <c r="W36" s="8">
         <v>865288</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="Y36" s="4">
         <f t="shared" si="31"/>
-        <v>186873</v>
+        <v>186883</v>
       </c>
       <c r="Z36" s="14">
-        <v>849783</v>
+        <v>849793</v>
       </c>
       <c r="AA36" s="5">
         <f t="shared" si="32"/>
-        <v>0.98208111056665526</v>
+        <v>0.98209266741246848</v>
       </c>
       <c r="AB36" s="8">
         <v>1522408</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="AD36" s="4">
         <f t="shared" si="33"/>
-        <v>327760</v>
+        <v>327773</v>
       </c>
       <c r="AE36" s="14">
-        <v>1515106</v>
+        <v>1515119</v>
       </c>
       <c r="AF36" s="5">
         <f t="shared" si="34"/>
-        <v>0.99520365105806063</v>
+        <v>0.99521219016190143</v>
       </c>
       <c r="AG36" s="8">
         <v>860909</v>
@@ -6687,14 +6687,14 @@
       </c>
       <c r="AI36" s="4">
         <f t="shared" si="35"/>
-        <v>196494</v>
+        <v>196506</v>
       </c>
       <c r="AJ36" s="14">
-        <v>856929</v>
+        <v>856941</v>
       </c>
       <c r="AK36" s="5">
         <f t="shared" si="36"/>
-        <v>0.9953769794484667</v>
+        <v>0.99539091820389847</v>
       </c>
       <c r="AL36" s="8">
         <v>879793</v>
@@ -6704,14 +6704,14 @@
       </c>
       <c r="AN36" s="4">
         <f t="shared" si="37"/>
-        <v>162061</v>
+        <v>162072</v>
       </c>
       <c r="AO36" s="14">
-        <v>866656</v>
+        <v>866667</v>
       </c>
       <c r="AP36" s="5">
         <f t="shared" si="38"/>
-        <v>0.9850680785139232</v>
+        <v>0.98508058145495592</v>
       </c>
       <c r="AQ36" s="8">
         <v>1539776</v>
@@ -6721,14 +6721,14 @@
       </c>
       <c r="AS36" s="4">
         <f t="shared" si="39"/>
-        <v>300093</v>
+        <v>300114</v>
       </c>
       <c r="AT36" s="14">
-        <v>1536704</v>
+        <v>1536725</v>
       </c>
       <c r="AU36" s="5">
         <f t="shared" si="40"/>
-        <v>0.99800490460950164</v>
+        <v>0.99801854295689763</v>
       </c>
       <c r="AV36" s="8">
         <v>875330</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="AX36" s="4">
         <f t="shared" si="41"/>
-        <v>161014</v>
+        <v>161030</v>
       </c>
       <c r="AY36" s="14">
-        <v>873851</v>
+        <v>873867</v>
       </c>
       <c r="AZ36" s="5">
         <f t="shared" si="42"/>
-        <v>0.99831035152456793</v>
+        <v>0.99832863034512698</v>
       </c>
       <c r="BA36" s="8">
         <v>893595</v>
@@ -6755,14 +6755,14 @@
       </c>
       <c r="BC36" s="4">
         <f t="shared" si="43"/>
-        <v>151822</v>
+        <v>151839</v>
       </c>
       <c r="BD36" s="14">
-        <v>884089</v>
+        <v>884106</v>
       </c>
       <c r="BE36" s="5">
         <f t="shared" si="44"/>
-        <v>0.98936207118437325</v>
+        <v>0.98938109546270958</v>
       </c>
       <c r="BF36" s="8">
         <v>1566403</v>
@@ -6772,14 +6772,14 @@
       </c>
       <c r="BH36" s="4">
         <f t="shared" si="45"/>
-        <v>365351</v>
+        <v>365378</v>
       </c>
       <c r="BI36" s="14">
-        <v>1557148</v>
+        <v>1557175</v>
       </c>
       <c r="BJ36" s="5">
         <f t="shared" si="46"/>
-        <v>0.99409155881340883</v>
+        <v>0.99410879575690292</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6797,14 +6797,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="0"/>
-        <v>131201</v>
+        <v>131206</v>
       </c>
       <c r="F37" s="14">
-        <v>667640</v>
+        <v>667645</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="24"/>
-        <v>0.98829248507510192</v>
+        <v>0.98829988646271405</v>
       </c>
       <c r="H37" s="8">
         <v>681828</v>
@@ -6814,14 +6814,14 @@
       </c>
       <c r="J37" s="4">
         <f t="shared" si="25"/>
-        <v>121659</v>
+        <v>121662</v>
       </c>
       <c r="K37" s="14">
-        <v>670324</v>
+        <v>670327</v>
       </c>
       <c r="L37" s="5">
         <f t="shared" si="26"/>
-        <v>0.98312770962764806</v>
+        <v>0.98313210956428898</v>
       </c>
       <c r="M37" s="8">
         <v>856106</v>
@@ -6831,14 +6831,14 @@
       </c>
       <c r="O37" s="4">
         <f t="shared" si="27"/>
-        <v>152394</v>
+        <v>152398</v>
       </c>
       <c r="P37" s="14">
-        <v>844600</v>
+        <v>844604</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" si="28"/>
-        <v>0.98656007550466884</v>
+        <v>0.98656474782328352</v>
       </c>
       <c r="R37" s="8">
         <v>679636</v>
@@ -6848,14 +6848,14 @@
       </c>
       <c r="T37" s="4">
         <f t="shared" si="29"/>
-        <v>129381</v>
+        <v>129385</v>
       </c>
       <c r="U37" s="14">
-        <v>671344</v>
+        <v>671348</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" si="30"/>
-        <v>0.98779935141752351</v>
+        <v>0.98780523692094002</v>
       </c>
       <c r="W37" s="8">
         <v>687189</v>
@@ -6865,14 +6865,14 @@
       </c>
       <c r="Y37" s="4">
         <f t="shared" si="31"/>
-        <v>131004</v>
+        <v>131010</v>
       </c>
       <c r="Z37" s="14">
-        <v>676138</v>
+        <v>676144</v>
       </c>
       <c r="AA37" s="5">
         <f t="shared" si="32"/>
-        <v>0.98391854351568486</v>
+        <v>0.98392727473809971</v>
       </c>
       <c r="AB37" s="8">
         <v>863912</v>
@@ -6882,14 +6882,14 @@
       </c>
       <c r="AD37" s="4">
         <f t="shared" si="33"/>
-        <v>163661</v>
+        <v>163671</v>
       </c>
       <c r="AE37" s="14">
-        <v>853784</v>
+        <v>853794</v>
       </c>
       <c r="AF37" s="5">
         <f t="shared" si="34"/>
-        <v>0.98827658372612026</v>
+        <v>0.98828815897915523</v>
       </c>
       <c r="AG37" s="8">
         <v>690763</v>
@@ -6899,14 +6899,14 @@
       </c>
       <c r="AI37" s="4">
         <f t="shared" si="35"/>
-        <v>132026</v>
+        <v>132034</v>
       </c>
       <c r="AJ37" s="14">
-        <v>682593</v>
+        <v>682601</v>
       </c>
       <c r="AK37" s="5">
         <f t="shared" si="36"/>
-        <v>0.98817249910606098</v>
+        <v>0.98818408050228512</v>
       </c>
       <c r="AL37" s="8">
         <v>697437</v>
@@ -6916,14 +6916,14 @@
       </c>
       <c r="AN37" s="4">
         <f t="shared" si="37"/>
-        <v>116230</v>
+        <v>116243</v>
       </c>
       <c r="AO37" s="14">
-        <v>688201</v>
+        <v>688214</v>
       </c>
       <c r="AP37" s="5">
         <f t="shared" si="38"/>
-        <v>0.98675722681761935</v>
+        <v>0.98677586649403459</v>
       </c>
       <c r="AQ37" s="8">
         <v>873380</v>
@@ -6933,14 +6933,14 @@
       </c>
       <c r="AS37" s="4">
         <f t="shared" si="39"/>
-        <v>150077</v>
+        <v>150094</v>
       </c>
       <c r="AT37" s="14">
-        <v>867366</v>
+        <v>867383</v>
       </c>
       <c r="AU37" s="5">
         <f t="shared" si="40"/>
-        <v>0.993114108406421</v>
+        <v>0.99313357301518235</v>
       </c>
       <c r="AV37" s="8">
         <v>700086</v>
@@ -6950,14 +6950,14 @@
       </c>
       <c r="AX37" s="4">
         <f t="shared" si="41"/>
-        <v>117149</v>
+        <v>117165</v>
       </c>
       <c r="AY37" s="14">
-        <v>694561</v>
+        <v>694577</v>
       </c>
       <c r="AZ37" s="5">
         <f t="shared" si="42"/>
-        <v>0.99210811243190122</v>
+        <v>0.99213096676694001</v>
       </c>
       <c r="BA37" s="8">
         <v>708485</v>
@@ -6967,14 +6967,14 @@
       </c>
       <c r="BC37" s="4">
         <f t="shared" si="43"/>
-        <v>113202</v>
+        <v>113218</v>
       </c>
       <c r="BD37" s="14">
-        <v>699074</v>
+        <v>699090</v>
       </c>
       <c r="BE37" s="5">
         <f t="shared" si="44"/>
-        <v>0.98671672653620046</v>
+        <v>0.98673930993599013</v>
       </c>
       <c r="BF37" s="8">
         <v>887779</v>
@@ -6984,14 +6984,14 @@
       </c>
       <c r="BH37" s="4">
         <f t="shared" si="45"/>
-        <v>186699</v>
+        <v>186726</v>
       </c>
       <c r="BI37" s="14">
-        <v>876534</v>
+        <v>876561</v>
       </c>
       <c r="BJ37" s="5">
         <f t="shared" si="46"/>
-        <v>0.98733355936556277</v>
+        <v>0.98736397233996298</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7009,14 +7009,14 @@
       </c>
       <c r="E38" s="4">
         <f t="shared" si="0"/>
-        <v>6081</v>
+        <v>6082</v>
       </c>
       <c r="F38" s="14">
-        <v>22915</v>
+        <v>22916</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="24"/>
-        <v>1.0078286493380832</v>
+        <v>1.0078726305141399</v>
       </c>
       <c r="H38" s="8">
         <v>23122</v>
@@ -7026,14 +7026,14 @@
       </c>
       <c r="J38" s="4">
         <f t="shared" si="25"/>
-        <v>5825</v>
+        <v>5826</v>
       </c>
       <c r="K38" s="14">
-        <v>23189</v>
+        <v>23190</v>
       </c>
       <c r="L38" s="5">
         <f t="shared" si="26"/>
-        <v>1.0028976732116599</v>
+        <v>1.0029409220655652</v>
       </c>
       <c r="M38" s="8">
         <v>35582</v>
@@ -7043,14 +7043,14 @@
       </c>
       <c r="O38" s="4">
         <f t="shared" si="27"/>
-        <v>9160</v>
+        <v>9161</v>
       </c>
       <c r="P38" s="14">
-        <v>35782</v>
+        <v>35783</v>
       </c>
       <c r="Q38" s="5">
         <f t="shared" si="28"/>
-        <v>1.0056208195154854</v>
+        <v>1.0056489236130628</v>
       </c>
       <c r="R38" s="8">
         <v>22911</v>
@@ -7060,14 +7060,14 @@
       </c>
       <c r="T38" s="4">
         <f t="shared" si="29"/>
-        <v>6111</v>
+        <v>6112</v>
       </c>
       <c r="U38" s="14">
-        <v>23141</v>
+        <v>23142</v>
       </c>
       <c r="V38" s="5">
         <f t="shared" si="30"/>
-        <v>1.0100388459691851</v>
+        <v>1.010082493125573</v>
       </c>
       <c r="W38" s="8">
         <v>23450</v>
@@ -7077,14 +7077,14 @@
       </c>
       <c r="Y38" s="4">
         <f t="shared" si="31"/>
-        <v>6343</v>
+        <v>6344</v>
       </c>
       <c r="Z38" s="14">
-        <v>23365</v>
+        <v>23366</v>
       </c>
       <c r="AA38" s="5">
         <f t="shared" si="32"/>
-        <v>0.99637526652452024</v>
+        <v>0.99641791044776118</v>
       </c>
       <c r="AB38" s="8">
         <v>35915</v>
@@ -7094,14 +7094,14 @@
       </c>
       <c r="AD38" s="4">
         <f t="shared" si="33"/>
-        <v>9133</v>
+        <v>9135</v>
       </c>
       <c r="AE38" s="14">
-        <v>36270</v>
+        <v>36272</v>
       </c>
       <c r="AF38" s="5">
         <f t="shared" si="34"/>
-        <v>1.0098844493944035</v>
+        <v>1.0099401364332452</v>
       </c>
       <c r="AG38" s="8">
         <v>23414</v>
@@ -7111,14 +7111,14 @@
       </c>
       <c r="AI38" s="4">
         <f t="shared" si="35"/>
-        <v>5995</v>
+        <v>5996</v>
       </c>
       <c r="AJ38" s="14">
-        <v>23667</v>
+        <v>23668</v>
       </c>
       <c r="AK38" s="5">
         <f t="shared" si="36"/>
-        <v>1.0108055009823183</v>
+        <v>1.0108482104723671</v>
       </c>
       <c r="AL38" s="8">
         <v>23927</v>
@@ -7128,14 +7128,14 @@
       </c>
       <c r="AN38" s="4">
         <f t="shared" si="37"/>
-        <v>5875</v>
+        <v>5876</v>
       </c>
       <c r="AO38" s="14">
-        <v>23920</v>
+        <v>23921</v>
       </c>
       <c r="AP38" s="5">
         <f t="shared" si="38"/>
-        <v>0.99970744347389973</v>
+        <v>0.99974923726334264</v>
       </c>
       <c r="AQ38" s="8">
         <v>36551</v>
@@ -7145,14 +7145,14 @@
       </c>
       <c r="AS38" s="4">
         <f t="shared" si="39"/>
-        <v>8726</v>
+        <v>8728</v>
       </c>
       <c r="AT38" s="14">
-        <v>37040</v>
+        <v>37042</v>
       </c>
       <c r="AU38" s="5">
         <f t="shared" si="40"/>
-        <v>1.0133785669338733</v>
+        <v>1.0134332849990424</v>
       </c>
       <c r="AV38" s="8">
         <v>23833</v>
@@ -7162,14 +7162,14 @@
       </c>
       <c r="AX38" s="4">
         <f t="shared" si="41"/>
-        <v>5579</v>
+        <v>5582</v>
       </c>
       <c r="AY38" s="14">
-        <v>24172</v>
+        <v>24175</v>
       </c>
       <c r="AZ38" s="5">
         <f t="shared" si="42"/>
-        <v>1.0142239751604918</v>
+        <v>1.0143498510468678</v>
       </c>
       <c r="BA38" s="8">
         <v>24292</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="BC38" s="4">
         <f t="shared" si="43"/>
-        <v>5307</v>
+        <v>5309</v>
       </c>
       <c r="BD38" s="14">
-        <v>24413</v>
+        <v>24415</v>
       </c>
       <c r="BE38" s="5">
         <f t="shared" si="44"/>
-        <v>1.004981063724683</v>
+        <v>1.005063395356496</v>
       </c>
       <c r="BF38" s="8">
         <v>37393</v>
@@ -7196,14 +7196,14 @@
       </c>
       <c r="BH38" s="4">
         <f t="shared" si="45"/>
-        <v>10303</v>
+        <v>10305</v>
       </c>
       <c r="BI38" s="14">
-        <v>37539</v>
+        <v>37541</v>
       </c>
       <c r="BJ38" s="5">
         <f t="shared" si="46"/>
-        <v>1.0039044740994303</v>
+        <v>1.003957960045998</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7433,14 +7433,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="0"/>
-        <v>58593</v>
+        <v>58596</v>
       </c>
       <c r="F40" s="14">
-        <v>275710</v>
+        <v>275713</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="24"/>
-        <v>0.99275534527333087</v>
+        <v>0.99276614744240643</v>
       </c>
       <c r="H40" s="8">
         <v>279588</v>
@@ -7450,14 +7450,14 @@
       </c>
       <c r="J40" s="4">
         <f t="shared" si="25"/>
-        <v>56625</v>
+        <v>56631</v>
       </c>
       <c r="K40" s="14">
-        <v>277372</v>
+        <v>277378</v>
       </c>
       <c r="L40" s="5">
         <f t="shared" si="26"/>
-        <v>0.99207405181910524</v>
+        <v>0.99209551196760948</v>
       </c>
       <c r="M40" s="8">
         <v>339205</v>
@@ -7467,14 +7467,14 @@
       </c>
       <c r="O40" s="4">
         <f t="shared" si="27"/>
-        <v>71976</v>
+        <v>71981</v>
       </c>
       <c r="P40" s="14">
-        <v>336835</v>
+        <v>336840</v>
       </c>
       <c r="Q40" s="5">
         <f t="shared" si="28"/>
-        <v>0.99301307468934719</v>
+        <v>0.99302781503810378</v>
       </c>
       <c r="R40" s="8">
         <v>280405</v>
@@ -7484,14 +7484,14 @@
       </c>
       <c r="T40" s="4">
         <f t="shared" si="29"/>
-        <v>61857</v>
+        <v>61863</v>
       </c>
       <c r="U40" s="14">
-        <v>278730</v>
+        <v>278736</v>
       </c>
       <c r="V40" s="5">
         <f t="shared" si="30"/>
-        <v>0.9940264973877071</v>
+        <v>0.99404789500900481</v>
       </c>
       <c r="W40" s="8">
         <v>283529</v>
@@ -7501,14 +7501,14 @@
       </c>
       <c r="Y40" s="4">
         <f t="shared" si="31"/>
-        <v>57467</v>
+        <v>57472</v>
       </c>
       <c r="Z40" s="14">
-        <v>280625</v>
+        <v>280630</v>
       </c>
       <c r="AA40" s="5">
         <f t="shared" si="32"/>
-        <v>0.98975766147378219</v>
+        <v>0.98977529635416484</v>
       </c>
       <c r="AB40" s="8">
         <v>342699</v>
@@ -7518,14 +7518,14 @@
       </c>
       <c r="AD40" s="4">
         <f t="shared" si="33"/>
-        <v>73660</v>
+        <v>73667</v>
       </c>
       <c r="AE40" s="14">
-        <v>341099</v>
+        <v>341106</v>
       </c>
       <c r="AF40" s="5">
         <f t="shared" si="34"/>
-        <v>0.9953311798400345</v>
+        <v>0.99535160592823435</v>
       </c>
       <c r="AG40" s="8">
         <v>284836</v>
@@ -7535,14 +7535,14 @@
       </c>
       <c r="AI40" s="4">
         <f t="shared" si="35"/>
-        <v>61254</v>
+        <v>61262</v>
       </c>
       <c r="AJ40" s="14">
-        <v>283346</v>
+        <v>283354</v>
       </c>
       <c r="AK40" s="5">
         <f t="shared" si="36"/>
-        <v>0.99476891965903191</v>
+        <v>0.99479700599643306</v>
       </c>
       <c r="AL40" s="8">
         <v>287465</v>
@@ -7552,14 +7552,14 @@
       </c>
       <c r="AN40" s="4">
         <f t="shared" si="37"/>
-        <v>57570</v>
+        <v>57581</v>
       </c>
       <c r="AO40" s="14">
-        <v>285437</v>
+        <v>285448</v>
       </c>
       <c r="AP40" s="5">
         <f t="shared" si="38"/>
-        <v>0.99294522811472696</v>
+        <v>0.99298349364270433</v>
       </c>
       <c r="AQ40" s="8">
         <v>346543</v>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="AS40" s="4">
         <f t="shared" si="39"/>
-        <v>69364</v>
+        <v>69376</v>
       </c>
       <c r="AT40" s="14">
-        <v>345854</v>
+        <v>345866</v>
       </c>
       <c r="AU40" s="5">
         <f t="shared" si="40"/>
-        <v>0.99801179074458291</v>
+        <v>0.99804641848197773</v>
       </c>
       <c r="AV40" s="8">
         <v>288959</v>
@@ -7586,14 +7586,14 @@
       </c>
       <c r="AX40" s="4">
         <f t="shared" si="41"/>
-        <v>60366</v>
+        <v>60377</v>
       </c>
       <c r="AY40" s="14">
-        <v>287672</v>
+        <v>287683</v>
       </c>
       <c r="AZ40" s="5">
         <f t="shared" si="42"/>
-        <v>0.99554608093189689</v>
+        <v>0.99558414861623967</v>
       </c>
       <c r="BA40" s="8">
         <v>291465</v>
@@ -7603,14 +7603,14 @@
       </c>
       <c r="BC40" s="4">
         <f t="shared" si="43"/>
-        <v>55979</v>
+        <v>55990</v>
       </c>
       <c r="BD40" s="14">
-        <v>288826</v>
+        <v>288837</v>
       </c>
       <c r="BE40" s="5">
         <f t="shared" si="44"/>
-        <v>0.990945739625684</v>
+        <v>0.99098348000617564</v>
       </c>
       <c r="BF40" s="8">
         <v>351557</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="BH40" s="4">
         <f t="shared" si="45"/>
-        <v>85164</v>
+        <v>85177</v>
       </c>
       <c r="BI40" s="14">
-        <v>348756</v>
+        <v>348769</v>
       </c>
       <c r="BJ40" s="5">
         <f t="shared" si="46"/>
-        <v>0.99203258646535275</v>
+        <v>0.99206956482163633</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7645,14 +7645,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="0"/>
-        <v>143406</v>
+        <v>143418</v>
       </c>
       <c r="F41" s="14">
-        <v>904693</v>
+        <v>904705</v>
       </c>
       <c r="G41" s="5">
         <f t="shared" si="24"/>
-        <v>0.99186395560204099</v>
+        <v>0.99187711185224658</v>
       </c>
       <c r="H41" s="8">
         <v>920596</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="J41" s="4">
         <f t="shared" si="25"/>
-        <v>139029</v>
+        <v>139041</v>
       </c>
       <c r="K41" s="14">
-        <v>909723</v>
+        <v>909735</v>
       </c>
       <c r="L41" s="5">
         <f t="shared" si="26"/>
-        <v>0.98818917310090415</v>
+        <v>0.98820220813473014</v>
       </c>
       <c r="M41" s="8">
         <v>1028922</v>
@@ -7679,14 +7679,14 @@
       </c>
       <c r="O41" s="4">
         <f t="shared" si="27"/>
-        <v>156600</v>
+        <v>156613</v>
       </c>
       <c r="P41" s="14">
-        <v>1016737</v>
+        <v>1016750</v>
       </c>
       <c r="Q41" s="5">
         <f t="shared" si="28"/>
-        <v>0.98815750853806217</v>
+        <v>0.9881701431206642</v>
       </c>
       <c r="R41" s="8">
         <v>924082</v>
@@ -7696,14 +7696,14 @@
       </c>
       <c r="T41" s="4">
         <f t="shared" si="29"/>
-        <v>157530</v>
+        <v>157543</v>
       </c>
       <c r="U41" s="14">
-        <v>914399</v>
+        <v>914412</v>
       </c>
       <c r="V41" s="5">
         <f t="shared" si="30"/>
-        <v>0.98952149268138545</v>
+        <v>0.98953556069699444</v>
       </c>
       <c r="W41" s="8">
         <v>929406</v>
@@ -7713,14 +7713,14 @@
       </c>
       <c r="Y41" s="4">
         <f t="shared" si="31"/>
-        <v>146273</v>
+        <v>146288</v>
       </c>
       <c r="Z41" s="14">
-        <v>918176</v>
+        <v>918191</v>
       </c>
       <c r="AA41" s="5">
         <f t="shared" si="32"/>
-        <v>0.98791701366248985</v>
+        <v>0.98793315300310092</v>
       </c>
       <c r="AB41" s="8">
         <v>1036539</v>
@@ -7730,14 +7730,14 @@
       </c>
       <c r="AD41" s="4">
         <f t="shared" si="33"/>
-        <v>166537</v>
+        <v>166562</v>
       </c>
       <c r="AE41" s="14">
-        <v>1025895</v>
+        <v>1025920</v>
       </c>
       <c r="AF41" s="5">
         <f t="shared" si="34"/>
-        <v>0.98973121127135588</v>
+        <v>0.98975532999723115</v>
       </c>
       <c r="AG41" s="8">
         <v>935526</v>
@@ -7747,14 +7747,14 @@
       </c>
       <c r="AI41" s="4">
         <f t="shared" si="35"/>
-        <v>150524</v>
+        <v>150541</v>
       </c>
       <c r="AJ41" s="14">
-        <v>924987</v>
+        <v>925004</v>
       </c>
       <c r="AK41" s="5">
         <f t="shared" si="36"/>
-        <v>0.98873467974166407</v>
+        <v>0.98875285133710877</v>
       </c>
       <c r="AL41" s="8">
         <v>940174</v>
@@ -7764,14 +7764,14 @@
       </c>
       <c r="AN41" s="4">
         <f t="shared" si="37"/>
-        <v>143255</v>
+        <v>143275</v>
       </c>
       <c r="AO41" s="14">
-        <v>929461</v>
+        <v>929481</v>
       </c>
       <c r="AP41" s="5">
         <f t="shared" si="38"/>
-        <v>0.98860530072093034</v>
+        <v>0.98862657337897031</v>
       </c>
       <c r="AQ41" s="8">
         <v>1046219</v>
@@ -7781,14 +7781,14 @@
       </c>
       <c r="AS41" s="4">
         <f t="shared" si="39"/>
-        <v>165660</v>
+        <v>165683</v>
       </c>
       <c r="AT41" s="14">
-        <v>1037547</v>
+        <v>1037570</v>
       </c>
       <c r="AU41" s="5">
         <f t="shared" si="40"/>
-        <v>0.99171110446283239</v>
+        <v>0.99173308838780405</v>
       </c>
       <c r="AV41" s="8">
         <v>945246</v>
@@ -7798,14 +7798,14 @@
       </c>
       <c r="AX41" s="4">
         <f t="shared" si="41"/>
-        <v>138790</v>
+        <v>138814</v>
       </c>
       <c r="AY41" s="14">
-        <v>936500</v>
+        <v>936524</v>
       </c>
       <c r="AZ41" s="5">
         <f t="shared" si="42"/>
-        <v>0.99074738216295022</v>
+        <v>0.99077277237883044</v>
       </c>
       <c r="BA41" s="8">
         <v>950318</v>
@@ -7815,14 +7815,14 @@
       </c>
       <c r="BC41" s="4">
         <f t="shared" si="43"/>
-        <v>134292</v>
+        <v>134317</v>
       </c>
       <c r="BD41" s="14">
-        <v>940097</v>
+        <v>940122</v>
       </c>
       <c r="BE41" s="5">
         <f t="shared" si="44"/>
-        <v>0.98924465284252217</v>
+        <v>0.98927095982607927</v>
       </c>
       <c r="BF41" s="8">
         <v>1056723</v>
@@ -7832,14 +7832,14 @@
       </c>
       <c r="BH41" s="4">
         <f t="shared" si="45"/>
-        <v>199533</v>
+        <v>199568</v>
       </c>
       <c r="BI41" s="14">
-        <v>1047509</v>
+        <v>1047544</v>
       </c>
       <c r="BJ41" s="5">
         <f t="shared" si="46"/>
-        <v>0.99128059103473665</v>
+        <v>0.99131371229735699</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8069,14 +8069,14 @@
       </c>
       <c r="E43" s="4">
         <f t="shared" si="0"/>
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="F43" s="14">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="G43" s="5">
         <f t="shared" si="24"/>
-        <v>0.99942112879884226</v>
+        <v>0.99971056439942108</v>
       </c>
       <c r="H43" s="8">
         <v>3541</v>
@@ -8086,14 +8086,14 @@
       </c>
       <c r="J43" s="4">
         <f t="shared" si="25"/>
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="K43" s="14">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="L43" s="5">
         <f t="shared" si="26"/>
-        <v>0.98192600960180743</v>
+        <v>0.98220841570177919</v>
       </c>
       <c r="M43" s="8">
         <v>4395</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="O43" s="4">
         <f t="shared" si="27"/>
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="P43" s="14">
-        <v>4341</v>
+        <v>4342</v>
       </c>
       <c r="Q43" s="5">
         <f t="shared" si="28"/>
-        <v>0.98771331058020473</v>
+        <v>0.98794084186575659</v>
       </c>
       <c r="R43" s="8">
         <v>3498</v>
@@ -8120,14 +8120,14 @@
       </c>
       <c r="T43" s="4">
         <f t="shared" si="29"/>
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="U43" s="14">
-        <v>3486</v>
+        <v>3487</v>
       </c>
       <c r="V43" s="5">
         <f t="shared" si="30"/>
-        <v>0.99656946826758153</v>
+        <v>0.99685534591194969</v>
       </c>
       <c r="W43" s="8">
         <v>3551</v>
@@ -8137,14 +8137,14 @@
       </c>
       <c r="Y43" s="4">
         <f t="shared" si="31"/>
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="Z43" s="14">
-        <v>3514</v>
+        <v>3515</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="32"/>
-        <v>0.98958039988735569</v>
+        <v>0.98986201070121094</v>
       </c>
       <c r="AB43" s="8">
         <v>4429</v>
@@ -8154,14 +8154,14 @@
       </c>
       <c r="AD43" s="4">
         <f t="shared" si="33"/>
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="AE43" s="14">
-        <v>4382</v>
+        <v>4383</v>
       </c>
       <c r="AF43" s="5">
         <f t="shared" si="34"/>
-        <v>0.98938812372996165</v>
+        <v>0.9896139083314518</v>
       </c>
       <c r="AG43" s="8">
         <v>3560</v>
@@ -8171,14 +8171,14 @@
       </c>
       <c r="AI43" s="4">
         <f t="shared" si="35"/>
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="AJ43" s="14">
-        <v>3547</v>
+        <v>3548</v>
       </c>
       <c r="AK43" s="5">
         <f t="shared" si="36"/>
-        <v>0.99634831460674156</v>
+        <v>0.99662921348314604</v>
       </c>
       <c r="AL43" s="8">
         <v>3588</v>
@@ -8188,14 +8188,14 @@
       </c>
       <c r="AN43" s="4">
         <f t="shared" si="37"/>
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="AO43" s="14">
-        <v>3584</v>
+        <v>3585</v>
       </c>
       <c r="AP43" s="5">
         <f t="shared" si="38"/>
-        <v>0.99888517279821631</v>
+        <v>0.99916387959866215</v>
       </c>
       <c r="AQ43" s="8">
         <v>4449</v>
@@ -8205,14 +8205,14 @@
       </c>
       <c r="AS43" s="4">
         <f t="shared" si="39"/>
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="AT43" s="14">
-        <v>4465</v>
+        <v>4466</v>
       </c>
       <c r="AU43" s="5">
         <f t="shared" si="40"/>
-        <v>1.0035963137783772</v>
+        <v>1.0038210833895258</v>
       </c>
       <c r="AV43" s="8">
         <v>3616</v>
@@ -8222,14 +8222,14 @@
       </c>
       <c r="AX43" s="4">
         <f t="shared" si="41"/>
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="AY43" s="14">
-        <v>3636</v>
+        <v>3637</v>
       </c>
       <c r="AZ43" s="5">
         <f t="shared" si="42"/>
-        <v>1.0055309734513274</v>
+        <v>1.0058075221238938</v>
       </c>
       <c r="BA43" s="8">
         <v>3655</v>
@@ -8239,14 +8239,14 @@
       </c>
       <c r="BC43" s="4">
         <f t="shared" si="43"/>
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="BD43" s="14">
-        <v>3651</v>
+        <v>3652</v>
       </c>
       <c r="BE43" s="5">
         <f t="shared" si="44"/>
-        <v>0.99890560875513001</v>
+        <v>0.99917920656634751</v>
       </c>
       <c r="BF43" s="8">
         <v>4544</v>
@@ -8256,14 +8256,14 @@
       </c>
       <c r="BH43" s="4">
         <f t="shared" si="45"/>
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="BI43" s="14">
-        <v>4540</v>
+        <v>4541</v>
       </c>
       <c r="BJ43" s="5">
         <f t="shared" si="46"/>
-        <v>0.99911971830985913</v>
+        <v>0.99933978873239437</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8281,14 +8281,14 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="0"/>
-        <v>76626</v>
+        <v>76627</v>
       </c>
       <c r="F44" s="14">
-        <v>333327</v>
+        <v>333328</v>
       </c>
       <c r="G44" s="5">
         <f t="shared" si="24"/>
-        <v>0.99137192619294046</v>
+        <v>0.99137490036522835</v>
       </c>
       <c r="H44" s="8">
         <v>340996</v>
@@ -8315,14 +8315,14 @@
       </c>
       <c r="O44" s="4">
         <f t="shared" si="27"/>
-        <v>87290</v>
+        <v>87291</v>
       </c>
       <c r="P44" s="14">
-        <v>404001</v>
+        <v>404002</v>
       </c>
       <c r="Q44" s="5">
         <f t="shared" si="28"/>
-        <v>0.98895748472505096</v>
+        <v>0.98895993263355786</v>
       </c>
       <c r="R44" s="8">
         <v>342556</v>
@@ -8332,14 +8332,14 @@
       </c>
       <c r="T44" s="4">
         <f t="shared" si="29"/>
-        <v>80313</v>
+        <v>80314</v>
       </c>
       <c r="U44" s="14">
-        <v>339401</v>
+        <v>339402</v>
       </c>
       <c r="V44" s="5">
         <f t="shared" si="30"/>
-        <v>0.99078982706477192</v>
+        <v>0.99079274629549619</v>
       </c>
       <c r="W44" s="8">
         <v>347597</v>
@@ -8349,14 +8349,14 @@
       </c>
       <c r="Y44" s="4">
         <f t="shared" si="31"/>
-        <v>79026</v>
+        <v>79028</v>
       </c>
       <c r="Z44" s="14">
-        <v>343169</v>
+        <v>343171</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="32"/>
-        <v>0.98726110984847393</v>
+        <v>0.9872668636380636</v>
       </c>
       <c r="AB44" s="8">
         <v>416340</v>
@@ -8366,14 +8366,14 @@
       </c>
       <c r="AD44" s="4">
         <f t="shared" si="33"/>
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="AE44" s="14">
-        <v>412369</v>
+        <v>412374</v>
       </c>
       <c r="AF44" s="5">
         <f t="shared" si="34"/>
-        <v>0.99046212230388619</v>
+        <v>0.9904741317192679</v>
       </c>
       <c r="AG44" s="8">
         <v>350469</v>
@@ -8383,14 +8383,14 @@
       </c>
       <c r="AI44" s="4">
         <f t="shared" si="35"/>
-        <v>79584</v>
+        <v>79590</v>
       </c>
       <c r="AJ44" s="14">
-        <v>347356</v>
+        <v>347362</v>
       </c>
       <c r="AK44" s="5">
         <f t="shared" si="36"/>
-        <v>0.99111761667936393</v>
+        <v>0.99113473659581874</v>
       </c>
       <c r="AL44" s="8">
         <v>355186</v>
@@ -8400,14 +8400,14 @@
       </c>
       <c r="AN44" s="4">
         <f t="shared" si="37"/>
-        <v>72544</v>
+        <v>72549</v>
       </c>
       <c r="AO44" s="14">
-        <v>350825</v>
+        <v>350830</v>
       </c>
       <c r="AP44" s="5">
         <f t="shared" si="38"/>
-        <v>0.98772192597681219</v>
+        <v>0.98773600310823062</v>
       </c>
       <c r="AQ44" s="8">
         <v>424208</v>
@@ -8417,14 +8417,14 @@
       </c>
       <c r="AS44" s="4">
         <f t="shared" si="39"/>
-        <v>85733</v>
+        <v>85740</v>
       </c>
       <c r="AT44" s="14">
-        <v>420969</v>
+        <v>420976</v>
       </c>
       <c r="AU44" s="5">
         <f t="shared" si="40"/>
-        <v>0.99236459472711502</v>
+        <v>0.99238109606608083</v>
       </c>
       <c r="AV44" s="8">
         <v>358114</v>
@@ -8434,14 +8434,14 @@
       </c>
       <c r="AX44" s="4">
         <f t="shared" si="41"/>
-        <v>72328</v>
+        <v>72334</v>
       </c>
       <c r="AY44" s="14">
-        <v>354443</v>
+        <v>354449</v>
       </c>
       <c r="AZ44" s="5">
         <f t="shared" si="42"/>
-        <v>0.98974907431711689</v>
+        <v>0.9897658287584401</v>
       </c>
       <c r="BA44" s="8">
         <v>361984</v>
@@ -8451,14 +8451,14 @@
       </c>
       <c r="BC44" s="4">
         <f t="shared" si="43"/>
-        <v>71215</v>
+        <v>71220</v>
       </c>
       <c r="BD44" s="14">
-        <v>357403</v>
+        <v>357408</v>
       </c>
       <c r="BE44" s="5">
         <f t="shared" si="44"/>
-        <v>0.98734474451909482</v>
+        <v>0.98735855728429989</v>
       </c>
       <c r="BF44" s="8">
         <v>432310</v>
@@ -8468,14 +8468,14 @@
       </c>
       <c r="BH44" s="4">
         <f t="shared" si="45"/>
-        <v>106886</v>
+        <v>106896</v>
       </c>
       <c r="BI44" s="14">
-        <v>427063</v>
+        <v>427073</v>
       </c>
       <c r="BJ44" s="5">
         <f t="shared" si="46"/>
-        <v>0.98786287617681756</v>
+        <v>0.98788600772593738</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8493,14 +8493,14 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="0"/>
-        <v>52303</v>
+        <v>52306</v>
       </c>
       <c r="F45" s="14">
-        <v>251297</v>
+        <v>251300</v>
       </c>
       <c r="G45" s="5">
         <f t="shared" si="24"/>
-        <v>0.98332668122304923</v>
+        <v>0.98333842024119766</v>
       </c>
       <c r="H45" s="8">
         <v>257610</v>
@@ -8510,14 +8510,14 @@
       </c>
       <c r="J45" s="4">
         <f t="shared" si="25"/>
-        <v>49787</v>
+        <v>49790</v>
       </c>
       <c r="K45" s="14">
-        <v>253170</v>
+        <v>253173</v>
       </c>
       <c r="L45" s="5">
         <f t="shared" si="26"/>
-        <v>0.98276464422964949</v>
+        <v>0.98277628974030506</v>
       </c>
       <c r="M45" s="8">
         <v>310366</v>
@@ -8527,14 +8527,14 @@
       </c>
       <c r="O45" s="4">
         <f t="shared" si="27"/>
-        <v>59540</v>
+        <v>59543</v>
       </c>
       <c r="P45" s="14">
-        <v>304812</v>
+        <v>304815</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" si="28"/>
-        <v>0.98210499861453893</v>
+        <v>0.98211466462176911</v>
       </c>
       <c r="R45" s="8">
         <v>257356</v>
@@ -8544,14 +8544,14 @@
       </c>
       <c r="T45" s="4">
         <f t="shared" si="29"/>
-        <v>53300</v>
+        <v>53304</v>
       </c>
       <c r="U45" s="14">
-        <v>253721</v>
+        <v>253725</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" si="30"/>
-        <v>0.98587559645005363</v>
+        <v>0.98589113912246074</v>
       </c>
       <c r="W45" s="8">
         <v>260553</v>
@@ -8561,14 +8561,14 @@
       </c>
       <c r="Y45" s="4">
         <f t="shared" si="31"/>
-        <v>55338</v>
+        <v>55342</v>
       </c>
       <c r="Z45" s="14">
-        <v>255682</v>
+        <v>255686</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="32"/>
-        <v>0.98130514712937478</v>
+        <v>0.98132049909231522</v>
       </c>
       <c r="AB45" s="8">
         <v>313911</v>
@@ -8578,14 +8578,14 @@
       </c>
       <c r="AD45" s="4">
         <f t="shared" si="33"/>
-        <v>65035</v>
+        <v>65041</v>
       </c>
       <c r="AE45" s="14">
-        <v>308442</v>
+        <v>308448</v>
       </c>
       <c r="AF45" s="5">
         <f t="shared" si="34"/>
-        <v>0.98257786442654127</v>
+        <v>0.98259697812437286</v>
       </c>
       <c r="AG45" s="8">
         <v>261210</v>
@@ -8595,14 +8595,14 @@
       </c>
       <c r="AI45" s="4">
         <f t="shared" si="35"/>
-        <v>53752</v>
+        <v>53757</v>
       </c>
       <c r="AJ45" s="14">
-        <v>257082</v>
+        <v>257087</v>
       </c>
       <c r="AK45" s="5">
         <f t="shared" si="36"/>
-        <v>0.98419662340645453</v>
+        <v>0.98421576509322006</v>
       </c>
       <c r="AL45" s="8">
         <v>264020</v>
@@ -8612,14 +8612,14 @@
       </c>
       <c r="AN45" s="4">
         <f t="shared" si="37"/>
-        <v>48990</v>
+        <v>48999</v>
       </c>
       <c r="AO45" s="14">
-        <v>259399</v>
+        <v>259408</v>
       </c>
       <c r="AP45" s="5">
         <f t="shared" si="38"/>
-        <v>0.98249753806529805</v>
+        <v>0.98253162639194003</v>
       </c>
       <c r="AQ45" s="8">
         <v>317407</v>
@@ -8629,14 +8629,14 @@
       </c>
       <c r="AS45" s="4">
         <f t="shared" si="39"/>
-        <v>63306</v>
+        <v>63315</v>
       </c>
       <c r="AT45" s="14">
-        <v>311496</v>
+        <v>311505</v>
       </c>
       <c r="AU45" s="5">
         <f t="shared" si="40"/>
-        <v>0.98137722230448599</v>
+        <v>0.98140557706666831</v>
       </c>
       <c r="AV45" s="8">
         <v>263886</v>
@@ -8646,14 +8646,14 @@
       </c>
       <c r="AX45" s="4">
         <f t="shared" si="41"/>
-        <v>51122</v>
+        <v>51129</v>
       </c>
       <c r="AY45" s="14">
-        <v>259548</v>
+        <v>259555</v>
       </c>
       <c r="AZ45" s="5">
         <f t="shared" si="42"/>
-        <v>0.98356108319501601</v>
+        <v>0.98358760980120208</v>
       </c>
       <c r="BA45" s="8">
         <v>265781</v>
@@ -8663,14 +8663,14 @@
       </c>
       <c r="BC45" s="4">
         <f t="shared" si="43"/>
-        <v>49575</v>
+        <v>49582</v>
       </c>
       <c r="BD45" s="14">
-        <v>261263</v>
+        <v>261270</v>
       </c>
       <c r="BE45" s="5">
         <f t="shared" si="44"/>
-        <v>0.9830010422114448</v>
+        <v>0.98302737968477805</v>
       </c>
       <c r="BF45" s="8">
         <v>319799</v>
@@ -8680,14 +8680,14 @@
       </c>
       <c r="BH45" s="4">
         <f t="shared" si="45"/>
-        <v>79760</v>
+        <v>79772</v>
       </c>
       <c r="BI45" s="14">
-        <v>314569</v>
+        <v>314581</v>
       </c>
       <c r="BJ45" s="5">
         <f t="shared" si="46"/>
-        <v>0.98364597762969863</v>
+        <v>0.98368350119919079</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9129,15 +9129,15 @@
       </c>
       <c r="E48" s="12">
         <f t="shared" ref="E48" si="47">F48-D48</f>
-        <v>1449961</v>
+        <v>1450047</v>
       </c>
       <c r="F48" s="11">
         <f>SUM(F10:F47)</f>
-        <v>7677656</v>
+        <v>7677742</v>
       </c>
       <c r="G48" s="13">
         <f t="shared" ref="G48" si="48">F48/C48</f>
-        <v>0.99549298170638101</v>
+        <v>0.99550413255716497</v>
       </c>
       <c r="H48" s="10">
         <f>SUM(H10:H47)</f>
@@ -9149,15 +9149,15 @@
       </c>
       <c r="J48" s="12">
         <f t="shared" si="25"/>
-        <v>1416335</v>
+        <v>1416427</v>
       </c>
       <c r="K48" s="11">
         <f>SUM(K10:K47)</f>
-        <v>7772970</v>
+        <v>7773062</v>
       </c>
       <c r="L48" s="13">
         <f t="shared" si="26"/>
-        <v>0.98800433793158149</v>
+        <v>0.98801603183997044</v>
       </c>
       <c r="M48" s="10">
         <f>SUM(M10:M47)</f>
@@ -9169,15 +9169,15 @@
       </c>
       <c r="O48" s="12">
         <f t="shared" si="27"/>
-        <v>2193179</v>
+        <v>2193292</v>
       </c>
       <c r="P48" s="11">
         <f>SUM(P10:P47)</f>
-        <v>12050236</v>
+        <v>12050349</v>
       </c>
       <c r="Q48" s="13">
         <f t="shared" si="28"/>
-        <v>0.99160517737782261</v>
+        <v>0.99161447606583542</v>
       </c>
       <c r="R48" s="10">
         <f>SUM(R10:R47)</f>
@@ -9189,15 +9189,15 @@
       </c>
       <c r="T48" s="12">
         <f t="shared" ref="T48" si="49">U48-S48</f>
-        <v>1489327</v>
+        <v>1489436</v>
       </c>
       <c r="U48" s="11">
         <f>SUM(U10:U47)</f>
-        <v>7743779</v>
+        <v>7743888</v>
       </c>
       <c r="V48" s="13">
         <f t="shared" si="30"/>
-        <v>0.9920426785250579</v>
+        <v>0.99205664233419544</v>
       </c>
       <c r="W48" s="10">
         <f>SUM(W10:W47)</f>
@@ -9209,15 +9209,15 @@
       </c>
       <c r="Y48" s="12">
         <f t="shared" si="31"/>
-        <v>1484891</v>
+        <v>1485013</v>
       </c>
       <c r="Z48" s="11">
         <f>SUM(Z10:Z47)</f>
-        <v>7828335</v>
+        <v>7828457</v>
       </c>
       <c r="AA48" s="13">
         <f t="shared" si="32"/>
-        <v>0.9849649545894974</v>
+        <v>0.98498030468941777</v>
       </c>
       <c r="AB48" s="10">
         <f>SUM(AB10:AB47)</f>
@@ -9229,15 +9229,15 @@
       </c>
       <c r="AD48" s="12">
         <f t="shared" si="33"/>
-        <v>2329435</v>
+        <v>2329653</v>
       </c>
       <c r="AE48" s="11">
         <f>SUM(AE10:AE47)</f>
-        <v>12196282</v>
+        <v>12196500</v>
       </c>
       <c r="AF48" s="13">
         <f t="shared" si="34"/>
-        <v>0.99284469886021687</v>
+        <v>0.99286244526394474</v>
       </c>
       <c r="AG48" s="10">
         <f>SUM(AG10:AG47)</f>
@@ -9249,15 +9249,15 @@
       </c>
       <c r="AI48" s="12">
         <f t="shared" si="35"/>
-        <v>1609083</v>
+        <v>1609247</v>
       </c>
       <c r="AJ48" s="11">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7875261</v>
+        <v>7875425</v>
       </c>
       <c r="AK48" s="13">
         <f t="shared" si="36"/>
-        <v>0.99254825767236432</v>
+        <v>0.99256892719865153</v>
       </c>
       <c r="AL48" s="10">
         <f>SUM(AL10:AL47)</f>
@@ -9269,15 +9269,15 @@
       </c>
       <c r="AN48" s="12">
         <f t="shared" si="37"/>
-        <v>1383113</v>
+        <v>1383305</v>
       </c>
       <c r="AO48" s="11">
         <f>SUM(AO10:AO47)</f>
-        <v>7957492</v>
+        <v>7957684</v>
       </c>
       <c r="AP48" s="13">
         <f t="shared" si="38"/>
-        <v>0.98502378604283947</v>
+        <v>0.98504755289889423</v>
       </c>
       <c r="AQ48" s="10">
         <f>SUM(AQ10:AQ47)</f>
@@ -9289,15 +9289,15 @@
       </c>
       <c r="AS48" s="12">
         <f t="shared" si="39"/>
-        <v>2139841</v>
+        <v>2140144</v>
       </c>
       <c r="AT48" s="11">
         <f>SUM(AT10:AT47)</f>
-        <v>12388558</v>
+        <v>12388861</v>
       </c>
       <c r="AU48" s="13">
         <f t="shared" si="40"/>
-        <v>0.9954450076760234</v>
+        <v>0.99546935432212424</v>
       </c>
       <c r="AV48" s="10">
         <f>SUM(AV10:AV47)</f>
@@ -9309,15 +9309,15 @@
       </c>
       <c r="AX48" s="12">
         <f t="shared" si="41"/>
-        <v>1373198</v>
+        <v>1373438</v>
       </c>
       <c r="AY48" s="11">
         <f>SUM(AY10:AY47)</f>
-        <v>8014413</v>
+        <v>8014653</v>
       </c>
       <c r="AZ48" s="13">
         <f t="shared" si="42"/>
-        <v>0.9941792526697808</v>
+        <v>0.99420902440984971</v>
       </c>
       <c r="BA48" s="10">
         <f>SUM(BA10:BA47)</f>
@@ -9329,15 +9329,15 @@
       </c>
       <c r="BC48" s="12">
         <f t="shared" si="43"/>
-        <v>1321477</v>
+        <v>1321722</v>
       </c>
       <c r="BD48" s="11">
         <f>SUM(BD10:BD47)</f>
-        <v>8098655</v>
+        <v>8098900</v>
       </c>
       <c r="BE48" s="13">
         <f t="shared" si="44"/>
-        <v>0.98734525212268764</v>
+        <v>0.9873751212289491</v>
       </c>
       <c r="BF48" s="10">
         <f>SUM(BF10:BF47)</f>
@@ -9349,15 +9349,15 @@
       </c>
       <c r="BH48" s="12">
         <f t="shared" si="45"/>
-        <v>2710519</v>
+        <v>2710950</v>
       </c>
       <c r="BI48" s="11">
         <f>SUM(BI10:BI47)</f>
-        <v>12557000</v>
+        <v>12557431</v>
       </c>
       <c r="BJ48" s="13">
         <f t="shared" si="46"/>
-        <v>0.99217291953419939</v>
+        <v>0.99220697436643002</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
@@ -9432,6 +9432,61 @@
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1"/>
+      <c r="X50" s="1"/>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+      <c r="AB50" s="1"/>
+      <c r="AC50" s="1"/>
+      <c r="AD50" s="1"/>
+      <c r="AE50" s="1"/>
+      <c r="AF50" s="1"/>
+      <c r="AG50" s="1"/>
+      <c r="AH50" s="1"/>
+      <c r="AI50" s="1"/>
+      <c r="AJ50" s="1"/>
+      <c r="AK50" s="1"/>
+      <c r="AL50" s="1"/>
+      <c r="AM50" s="1"/>
+      <c r="AN50" s="1"/>
+      <c r="AO50" s="1"/>
+      <c r="AP50" s="1"/>
+      <c r="AQ50" s="1"/>
+      <c r="AR50" s="1"/>
+      <c r="AS50" s="1"/>
+      <c r="AT50" s="1"/>
+      <c r="AU50" s="1"/>
+      <c r="AV50" s="1"/>
+      <c r="AW50" s="1"/>
+      <c r="AX50" s="1"/>
+      <c r="AY50" s="1"/>
+      <c r="AZ50" s="1"/>
+      <c r="BA50" s="1"/>
+      <c r="BB50" s="1"/>
+      <c r="BC50" s="1"/>
+      <c r="BD50" s="1"/>
+      <c r="BE50" s="1"/>
+      <c r="BF50" s="1"/>
+      <c r="BG50" s="1"/>
+      <c r="BH50" s="1"/>
+      <c r="BI50" s="1"/>
+      <c r="BJ50" s="1"/>
     </row>
     <row r="51" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
